--- a/results/job_matches_2026-06-27.xlsx
+++ b/results/job_matches_2026-06-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G137"/>
+  <dimension ref="A1:G100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,17 +713,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior API Cloud Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Transflo</t>
+          <t>WSSC Water</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Laurel, MD, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Blob Storage, GCP, Hadoop</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,19 +741,19 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6877ccbd8db8810</t>
+          <t>https://www.indeed.com/viewjob?jk=efacd6764e780443</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior API Cloud Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>U.S. Financial Technology</t>
+          <t>Transflo</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a593e5a13bf91848</t>
+          <t>https://www.indeed.com/viewjob?jk=c6877ccbd8db8810</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>WSSC Water</t>
+          <t>U.S. Financial Technology</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Laurel, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,17 +801,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Blob Storage, GCP, Hadoop</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efacd6764e780443</t>
+          <t>https://www.indeed.com/viewjob?jk=a593e5a13bf91848</t>
         </is>
       </c>
     </row>
@@ -888,17 +888,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr. IT Big Data Developer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Diverse Agile Solutions</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL</t>
+          <t>AWS, Lambda, Kinesis, Athena, IAM, RDS, Databricks, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dba4bfa4195a614f</t>
+          <t>https://www.indeed.com/viewjob?jk=feff26b7bae36907</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Architect – Washington, DC</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Creative Information Technology India</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Falls Church, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL</t>
+          <t>AWS, Lambda, Kinesis, Athena, IAM, RDS, Databricks, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94d5786e7c110147</t>
+          <t>https://www.indeed.com/viewjob?jk=694cbe94ae40ae5b</t>
         </is>
       </c>
     </row>
@@ -963,20 +963,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>retail services &amp; systems</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake, Dimensional Modeling, ETL</t>
+          <t>AWS, Lambda, Kinesis, Athena, IAM, RDS, Databricks, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f105ffde2d1f4df</t>
+          <t>https://www.indeed.com/viewjob?jk=a0f4bf7cb698e418</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior IT Big Data Developer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Centurion Consulting Group</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, Lambda, Kinesis, Athena, IAM, RDS, Databricks, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae26c12caca27959</t>
+          <t>https://www.indeed.com/viewjob?jk=48492fee574585c7</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior IT Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Centurion Consulting Group</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, Lambda, Kinesis, Athena, IAM, RDS, Databricks, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efb360d7f7dedcd5</t>
+          <t>https://www.indeed.com/viewjob?jk=6a3e9b920b8a4519</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer Senior - Big Data Platform Team</t>
+          <t>Data Architect – Washington, DC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Creative Information Technology India</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Farmers Branch, TX, US USA</t>
+          <t>Falls Church, VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Spark, Scala, Data Modeling, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Step Functions, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,67 +1091,67 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bd359ddd135794e</t>
+          <t>https://www.indeed.com/viewjob?jk=94d5786e7c110147</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer III (US)</t>
+          <t>Sr. IT Big Data Developer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>Diverse Agile Solutions</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Google Cloud Platform, Spark, PySpark, Scala</t>
+          <t>AWS, Step Functions, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3f872ac99e6bd1a</t>
+          <t>https://www.indeed.com/viewjob?jk=dba4bfa4195a614f</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Enterprise Data Services</t>
+          <t>Senior IT Big Data Developer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Wellmark Blue Cross and Blue Shield</t>
+          <t>Centurion Consulting Group</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, RDS</t>
+          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96ed3a70f59cd7a0</t>
+          <t>https://www.indeed.com/viewjob?jk=ae26c12caca27959</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Architect (173743)</t>
+          <t>Data Engineer Senior - Big Data Platform Team</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Farmers Branch, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, Scala, Snowflake, Oracle</t>
+          <t>S3, RDS, Azure, Spark, Scala, Data Modeling, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9545b3f6e705f68</t>
+          <t>https://www.indeed.com/viewjob?jk=0bd359ddd135794e</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Consultant- Data/AI Due Diligence-MTS</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>retail services &amp; systems</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
+          <t>RDS, Databricks, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b6bc1ec4cda3c8e</t>
+          <t>https://www.indeed.com/viewjob?jk=0f105ffde2d1f4df</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior IT Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Energy Services Group</t>
+          <t>Centurion Consulting Group</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22692d347007686c</t>
+          <t>https://www.indeed.com/viewjob?jk=efb360d7f7dedcd5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Engineer, Invest Tech</t>
+          <t>Senior Software Engineer - Platform</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=418fe6804d9bbee5</t>
+          <t>https://www.indeed.com/viewjob?jk=3ecc89ba914fc587</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Engineer, Invest Tech</t>
+          <t>Senior Software Engineer - Enterprise Data Services</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>Wellmark Blue Cross and Blue Shield</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, RDS</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=455cbc0d06bec7dd</t>
+          <t>https://www.indeed.com/viewjob?jk=96ed3a70f59cd7a0</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>Software Engineer III (US)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Google Cloud Platform, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=861d82e3c9e267af</t>
+          <t>https://www.indeed.com/viewjob?jk=d3f872ac99e6bd1a</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Data Architect (173743)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32c289c0954d3b83</t>
+          <t>https://www.indeed.com/viewjob?jk=c9545b3f6e705f68</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Senior Consultant- Data/AI Due Diligence-MTS</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=563ad203b5a2853e</t>
+          <t>https://www.indeed.com/viewjob?jk=7b6bc1ec4cda3c8e</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Senior Engineer, Invest Tech</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c88857b2990a629</t>
+          <t>https://www.indeed.com/viewjob?jk=efdcc6d0c28ecda9</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Energy Services Group</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,19 +1511,19 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c30d6189ed53ff4</t>
+          <t>https://www.indeed.com/viewjob?jk=22692d347007686c</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Senior Engineer, Invest Tech</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9f1090e8d875682</t>
+          <t>https://www.indeed.com/viewjob?jk=418fe6804d9bbee5</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Senior Engineer, Invest Tech</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09009f7e617a8382</t>
+          <t>https://www.indeed.com/viewjob?jk=455cbc0d06bec7dd</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3c113a0ea31c0ed</t>
+          <t>https://www.indeed.com/viewjob?jk=861d82e3c9e267af</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5962eb966972f6e</t>
+          <t>https://www.indeed.com/viewjob?jk=32c289c0954d3b83</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b49f50dbf2988c82</t>
+          <t>https://www.indeed.com/viewjob?jk=563ad203b5a2853e</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d75b791cf50c1184</t>
+          <t>https://www.indeed.com/viewjob?jk=9c88857b2990a629</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=776060619ca92d8b</t>
+          <t>https://www.indeed.com/viewjob?jk=6c30d6189ed53ff4</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2362abd894783c27</t>
+          <t>https://www.indeed.com/viewjob?jk=c9f1090e8d875682</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=992a2c5f94075440</t>
+          <t>https://www.indeed.com/viewjob?jk=09009f7e617a8382</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Full Stack</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69e822c1cf66e308</t>
+          <t>https://www.indeed.com/viewjob?jk=b3c113a0ea31c0ed</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Full Stack</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37dbcc8bf6973335</t>
+          <t>https://www.indeed.com/viewjob?jk=d5962eb966972f6e</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d84fecedb12dd363</t>
+          <t>https://www.indeed.com/viewjob?jk=69e822c1cf66e308</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abe999fc3b54fcb4</t>
+          <t>https://www.indeed.com/viewjob?jk=37dbcc8bf6973335</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Full-Stack Java Developer</t>
+          <t>Software Engineer 2 - Full Stack</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,42 +1991,42 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Blob Storage, Scala, Kafka, PostgreSQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=651520622efc1265</t>
+          <t>https://www.indeed.com/viewjob?jk=d84fecedb12dd363</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Platform Engineer (Associate)</t>
+          <t>Software Engineer 2 - Full Stack</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,54 +2036,54 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52b81f936f231329</t>
+          <t>https://www.indeed.com/viewjob?jk=abe999fc3b54fcb4</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Engineering</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Fubo</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e24be3cd83341f1</t>
+          <t>https://www.indeed.com/viewjob?jk=b49f50dbf2988c82</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Arc Technologies Group</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2092,143 +2092,143 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ccc63169a66ef59</t>
+          <t>https://www.indeed.com/viewjob?jk=d75b791cf50c1184</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Remote Kubernetes Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Cloud Data Vision</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5be313cc3b61a58</t>
+          <t>https://www.indeed.com/viewjob?jk=776060619ca92d8b</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>New York City Department of Sanitation</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Informatica PowerCenter, Oracle, Data Modeling, ETL, ELT, Pentaho</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f58c8be3a69d599b</t>
+          <t>https://www.indeed.com/viewjob?jk=2362abd894783c27</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Robotics Data Engineer/Data Scientist</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Spark Streaming, Kafka, PostgreSQL, Cassandra, Data Modeling</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7d4e995adafbb96</t>
+          <t>https://www.indeed.com/viewjob?jk=992a2c5f94075440</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>Fubo</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d54d860c68542f20</t>
+          <t>https://www.indeed.com/viewjob?jk=0e24be3cd83341f1</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>IT Software Engineer II</t>
+          <t>Senior Robotics Data Engineer/Data Scientist</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Yusen Logistics</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Spark Streaming, Kafka, PostgreSQL, Cassandra, Data Modeling</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d97e3542d74962da</t>
+          <t>https://www.indeed.com/viewjob?jk=f7d4e995adafbb96</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>IT Software Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Yusen Logistics</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef2fe730515dbece</t>
+          <t>https://www.indeed.com/viewjob?jk=8122e2600ab1407a</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Data Platform Engineer (Associate)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac0b8be0e4857da6</t>
+          <t>https://www.indeed.com/viewjob?jk=52b81f936f231329</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr Data Scientist - Member Growth &amp; Prescreen Modeling</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>Arc Technologies Group</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Tukwila, WA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Snowflake, MLOps</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93bbd48d3322e5c7</t>
+          <t>https://www.indeed.com/viewjob?jk=8ccc63169a66ef59</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Developer Operations Engineer I</t>
+          <t>Remote Kubernetes Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Transcor Data Services</t>
+          <t>Cloud Data Vision</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b84e13a37c8822b9</t>
+          <t>https://www.indeed.com/viewjob?jk=b5be313cc3b61a58</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>El Pollo Loco</t>
+          <t>New York City Department of Sanitation</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, SQL Server, DynamoDB, CI/CD</t>
+          <t>RDS, Databricks, Spark, PySpark, Informatica PowerCenter, Oracle, Data Modeling, ETL, ELT, Pentaho</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bd72bf197f82e23</t>
+          <t>https://www.indeed.com/viewjob?jk=f58c8be3a69d599b</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Orchestration</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Arvest Bank</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Dataflow, Scala, Kafka, ETL, dbt, Tableau, Docker</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8fe7267b8b9de10</t>
+          <t>https://www.indeed.com/viewjob?jk=d54d860c68542f20</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>IT Software Engineer II</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Univision Communications Inc</t>
+          <t>Yusen Logistics</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, IAM, Google Cloud Platform, GCP, Hadoop, Spark, Scala, dbt, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2f885fbfd483879</t>
+          <t>https://www.indeed.com/viewjob?jk=d97e3542d74962da</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer, League Analytics &amp; Infrastructure</t>
+          <t>IT Software Engineer II</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Major League Baseball</t>
+          <t>Yusen Logistics</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e63e2ea97ff196b</t>
+          <t>https://www.indeed.com/viewjob?jk=ef2fe730515dbece</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Hybrid</t>
+          <t>Sr Data Scientist - Member Growth &amp; Prescreen Modeling</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Tukwila, WA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Google Cloud Platform, GCP</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c3e33c47a701cd2</t>
+          <t>https://www.indeed.com/viewjob?jk=93bbd48d3322e5c7</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Hybrid</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Google Cloud Platform, GCP</t>
+          <t>Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e620dabe0cd123</t>
+          <t>https://www.indeed.com/viewjob?jk=ac0b8be0e4857da6</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Engineer | Middleware</t>
+          <t>Developer Operations Engineer I</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ExtraHop Networks</t>
+          <t>Transcor Data Services</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, IAM, RDS, Azure, GCP, Scala, PostgreSQL, Terraform</t>
+          <t>AWS, RDS, Azure, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=111ecbafdd773723</t>
+          <t>https://www.indeed.com/viewjob?jk=b84e13a37c8822b9</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Univision Communications Inc</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, IAM, Google Cloud Platform, GCP, Hadoop, Spark, Scala, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b9a38e235659081</t>
+          <t>https://www.indeed.com/viewjob?jk=b2f885fbfd483879</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>Data Platform Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, CI/CD, Kubernetes, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd0775a42f899524</t>
+          <t>https://www.indeed.com/viewjob?jk=a25c9133cd0e70a2</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>El Pollo Loco</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, SQL Server, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b33138f7850dfefc</t>
+          <t>https://www.indeed.com/viewjob?jk=8bd72bf197f82e23</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>Senior Software Engineer - SRE Focus</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>CNH Industrial</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>Sioux Falls, SD, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, MongoDB, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a342726a84e27f8e</t>
+          <t>https://www.indeed.com/viewjob?jk=d07053a0ea5ac768</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>Senior Data Engineer - Orchestration</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Arvest Bank</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, GCP, Dataflow, Scala, Kafka, ETL, dbt, Tableau, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c186d8b7ac65fdf8</t>
+          <t>https://www.indeed.com/viewjob?jk=e8fe7267b8b9de10</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>Data Engineer, League Analytics &amp; Infrastructure</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Major League Baseball</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95cc142f3e2617a6</t>
+          <t>https://www.indeed.com/viewjob?jk=5e63e2ea97ff196b</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>Senior Software Engineer - Hybrid</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Google Cloud Platform, GCP</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db16f20add9ea986</t>
+          <t>https://www.indeed.com/viewjob?jk=6c3e33c47a701cd2</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>Senior Software Engineer - Hybrid</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Google Cloud Platform, GCP</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1382d06b80fb6867</t>
+          <t>https://www.indeed.com/viewjob?jk=03e620dabe0cd123</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Ameriprise Financial</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Dataflow, Oracle, SQL Server, PostgreSQL, ETL, MLOps</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcad5c4e643319ff</t>
+          <t>https://www.indeed.com/viewjob?jk=2dc316693a524ae7</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>Senior Software Engineer | Middleware</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>ExtraHop Networks</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, S3, SQS, IAM, RDS, Azure, GCP, Scala, PostgreSQL, Terraform</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40e64526422d931b</t>
+          <t>https://www.indeed.com/viewjob?jk=111ecbafdd773723</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>Senior Big Data Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4d627fd3422104c</t>
+          <t>https://www.indeed.com/viewjob?jk=a57c804e0f6cdd8d</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>Senior AI Software Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Bosch</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>Plymouth, MI, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Scala, MLOps, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fab8211cf6bde1e0</t>
+          <t>https://www.indeed.com/viewjob?jk=f03c5058699b33f7</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>Junior Analytics Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>SewerAI</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Walnut Creek, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Redshift, S3, IAM, RDS, BigQuery, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05bab721c73d545f</t>
+          <t>https://www.indeed.com/viewjob?jk=ef23c8da578678cc</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>Data Engineer - 2 Openings</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Blood Cancer United</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, S3, RDS, Azure, Blob Storage, GCP, Scala, Snowflake, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85a706af297ba804</t>
+          <t>https://www.indeed.com/viewjob?jk=dd9f154e39bab643</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>Python AI Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>Kafka, PostgreSQL, ETL, CI/CD, Jenkins, Maven, Docker, Jenkins, pytest, Airflow</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,67 +3191,67 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13401bc8d0f3279e</t>
+          <t>https://www.indeed.com/viewjob?jk=277d01c969e4d645</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>Sr BI Analyst</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Mizkan America</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>RDS, Azure, Synapse Analytics, Dataflow, Spark, PySpark, Scala, Data Modeling, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31032458d140d1ae</t>
+          <t>https://www.indeed.com/viewjob?jk=4207b3535cb26a9b</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>Sr RPA Process Automation Developer (UIPATH)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=115cfe00112809d8</t>
+          <t>https://www.indeed.com/viewjob?jk=23d1d78d2eac45da</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>Senior .net Software Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>Azure, Spark, Scala, SQL Server, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=031a5b8865d1f458</t>
+          <t>https://www.indeed.com/viewjob?jk=2ec84c14bbe42215</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Wausau, WI, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Kafka, Snowflake, Oracle, ETL, CI/CD, Jenkins, Jenkins, Airflow</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65c6bb88e77fa7e3</t>
+          <t>https://www.indeed.com/viewjob?jk=f2a4a5c971b6dae8</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,67 +3366,67 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0426526011ecf8ab</t>
+          <t>https://www.indeed.com/viewjob?jk=276c91b178e50bc3</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>Sr. Software Engineer, Enterprise Software</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, NoSQL, Splunk, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2f4ae59bb2e76db</t>
+          <t>https://www.indeed.com/viewjob?jk=424a613517dace69</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc596e52195e0933</t>
+          <t>https://www.indeed.com/viewjob?jk=d930f40a8264fcae</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>MuleSoft QA Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44f8b5180e01e140</t>
+          <t>https://www.indeed.com/viewjob?jk=8ec42b333047dabf</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>Sustainability Data and AI Consultant</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Git, Python</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af0b8f364ebc3247</t>
+          <t>https://www.indeed.com/viewjob?jk=bc927e4fc5649b27</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>Software Engineer ll, Data Platform</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Cohere Health</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, EMR, Athena, S3, RDS, Scala, Kafka, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef9c01896959f630</t>
+          <t>https://www.indeed.com/viewjob?jk=80e694b601457a09</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>Sustainability Data and AI Consultant</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Git, Python</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=271061dada6a961f</t>
+          <t>https://www.indeed.com/viewjob?jk=7976a31d4fb905fe</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Lake Buena Vista, FL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, S3, Databricks, Kafka, Snowflake, PostgreSQL, Data Modeling, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1faf6e04fa2bbdcf</t>
+          <t>https://www.indeed.com/viewjob?jk=0309d0101fc2195f</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9794568eb039870</t>
+          <t>https://www.indeed.com/viewjob?jk=04b2fdcc099c4491</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>AI Engineer III</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Visual Comfort &amp; Co</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1560887d7cb316fd</t>
+          <t>https://www.indeed.com/viewjob?jk=ed6f23c724c8deb1</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>MuleSoft Developer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, Oracle, SQL Server, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdd4ac5f09111b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=2aedb694782bdb77</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>Digital Services Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Continental</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>Clinton, MD, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, NoSQL, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dee274917e4b9029</t>
+          <t>https://www.indeed.com/viewjob?jk=92b28fa10f3665b6</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Blaine, MN, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,67 +3786,67 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c1f0804f082a435</t>
+          <t>https://www.indeed.com/viewjob?jk=171a3405a6bf87d5</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>AI Systems Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, SQS, SNS, IAM, RDS, Databricks, Scala, Kafka, Databricks Lakehouse, NoSQL</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bcfef10dd24abe4</t>
+          <t>https://www.indeed.com/viewjob?jk=c00f3c6eabf7aab0</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>Software Engineering Supervisor - Hybrid</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Sunrise Banks</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, NoSQL, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,32 +3856,32 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71d3b83605c8a2df</t>
+          <t>https://www.indeed.com/viewjob?jk=853197679fd8570c</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>Senior Software Engineer - Python/Agentic AI</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>BlackLine</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Kafka, PostgreSQL, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,32 +3891,32 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=940dcb7683294d7b</t>
+          <t>https://www.indeed.com/viewjob?jk=2f2ba4e75ec79621</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>Security Platform Engineer 2 (Hybrid - Seattle)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3925,1301 +3925,6 @@
         </is>
       </c>
       <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fbb60bebb7779e64</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Software Engineer - Search and Personalization</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>SD, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c37d2114cee6dba4</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Software Engineer - Search and Personalization</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>MI, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c39c8b726cdb22aa</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Software Engineer - Search and Personalization</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>MA, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bd9a756aa23e011c</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Software Engineer - Search and Personalization</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>WV, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=22d070dab1e1cb93</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Software Engineer - Search and Personalization</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>MD, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4045cf1c680be7b6</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Software Engineer - Search and Personalization</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>ID, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d5f4daad7fda9ff7</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Software Engineer - Search and Personalization</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>MO, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d0671107537ae859</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Software Engineer - Search and Personalization</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>ME, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a057a8d1dc27a54f</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Software Engineer - Search and Personalization</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>UT, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3ec8eebe082d41ed</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Software Engineer - Search and Personalization</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>OR, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3912346602551520</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Software Engineer - Search and Personalization</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>AL, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0c6b2ae9b514e3c3</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Software Engineer - Search and Personalization</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>CO, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cdeb6923f62c2160</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Software Engineer - Search and Personalization</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>RI, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e8bc2ea076a0ded7</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Software Engineer - Search and Personalization</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>MT, US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Docker</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ee0fd3306ac2ce34</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Junior Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>SewerAI</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Walnut Creek, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, S3, IAM, RDS, BigQuery, Snowflake, ETL, ELT, dbt</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ef23c8da578678cc</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Senior Big Data Software Engineer - Remote</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Eden Prairie, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a57c804e0f6cdd8d</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Data Engineer - 2 Openings</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Blood Cancer United</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, Blob Storage, GCP, Scala, Snowflake, Data Modeling, Kimball</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dd9f154e39bab643</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Senior AI Software Engineer</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Bosch</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Plymouth, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Scala, MLOps, CI/CD, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f03c5058699b33f7</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Sr BI Analyst</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Mizkan America</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Synapse Analytics, Dataflow, Spark, PySpark, Scala, Data Modeling, Power BI, CI/CD</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4207b3535cb26a9b</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Analytics Developer, Enterprise Analytics (Data Shared Services)</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>NewYork-Presbyterian Hospital</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Manhattan, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ELT, Power BI, Azure DevOps, Git</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a889968da2ddc13e</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Wausau, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Kafka, Snowflake, Oracle, ETL, CI/CD, Jenkins, Jenkins, Airflow</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f2a4a5c971b6dae8</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Senior .net Software Engineer</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Wells Fargo</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>Azure, Spark, Scala, SQL Server, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2ec84c14bbe42215</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Minnetonka, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=276c91b178e50bc3</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer, Enterprise Software</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Rivian</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, NoSQL, Splunk, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=424a613517dace69</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Sustainability Data and AI Consultant</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Git, Python</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bc927e4fc5649b27</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Software Engineer ll, Data Platform</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Cohere Health</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>AWS, EMR, Athena, S3, RDS, Scala, Kafka, dbt, CI/CD, Airflow</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=80e694b601457a09</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Sustainability Data and AI Consultant</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Git, Python</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7976a31d4fb905fe</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>The Walt Disney Company</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Lake Buena Vista, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>AWS, S3, Databricks, Kafka, Snowflake, PostgreSQL, Data Modeling, Docker, Kubernetes, Airflow</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0309d0101fc2195f</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>MuleSoft QA Engineer</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>UniFirst</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Wilmington, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8ec42b333047dabf</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>AI Engineer III</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Visual Comfort &amp; Co</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI, Python</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ed6f23c724c8deb1</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>MuleSoft Developer</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>UniFirst</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Wilmington, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, Oracle, SQL Server, NoSQL, Splunk, CI/CD</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2aedb694782bdb77</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Digital Services Engineer</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Continental</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Clinton, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D132" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, NoSQL, Docker, Kubernetes, Git, Python</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=92b28fa10f3665b6</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Snowflake Architect</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Cognizant</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Blaine, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=171a3405a6bf87d5</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>AI Systems Engineer</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Suffolk Construction</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>AWS, SQS, SNS, IAM, RDS, Databricks, Scala, Kafka, Databricks Lakehouse, NoSQL</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c00f3c6eabf7aab0</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Software Engineering Supervisor - Hybrid</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Sunrise Banks</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Saint Paul, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D135" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, NoSQL, CI/CD, Azure DevOps, Git</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=853197679fd8570c</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Python/Agentic AI</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>BlackLine</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Pleasanton, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D136" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Kafka, PostgreSQL, NoSQL, Docker</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2f2ba4e75ec79621</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Security Platform Engineer 2 (Hybrid - Seattle)</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Nordstrom</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D137" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=49744f4cb7f46ca9</t>
         </is>

--- a/results/job_matches_2026-06-27.xlsx
+++ b/results/job_matches_2026-06-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G100"/>
+  <dimension ref="A1:G102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -783,12 +783,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Mainframe Analyst (Healthcare)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>U.S. Financial Technology</t>
+          <t>NSV IT SOLUTIONS</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -801,69 +801,69 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a593e5a13bf91848</t>
+          <t>https://www.indeed.com/viewjob?jk=529186dc1f0e5461</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Mainframe Analyst (Healthcare)</t>
+          <t>Senior IT Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NSV IT SOLUTIONS</t>
+          <t>Diverse Agile Solutions</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=529186dc1f0e5461</t>
+          <t>https://www.indeed.com/viewjob?jk=445f550d4f69a7c6</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior IT Data Engineer</t>
+          <t>Quant Analytics Associate Sr - DART</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Diverse Agile Solutions</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,17 +871,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, ETL, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=445f550d4f69a7c6</t>
+          <t>https://www.indeed.com/viewjob?jk=958563c6ca41d7c8</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Robotics Data Engineer/Data Scientist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Spark Streaming, Kafka, PostgreSQL, Cassandra, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7d4e995adafbb96</t>
+          <t>https://www.indeed.com/viewjob?jk=8122e2600ab1407a</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Platform Engineer (Associate)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8122e2600ab1407a</t>
+          <t>https://www.indeed.com/viewjob?jk=52b81f936f231329</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Platform Engineer (Associate)</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>Arc Technologies Group</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52b81f936f231329</t>
+          <t>https://www.indeed.com/viewjob?jk=8ccc63169a66ef59</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Remote Kubernetes Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Arc Technologies Group</t>
+          <t>Cloud Data Vision</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ccc63169a66ef59</t>
+          <t>https://www.indeed.com/viewjob?jk=b5be313cc3b61a58</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Remote Kubernetes Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Cloud Data Vision</t>
+          <t>New York City Department of Sanitation</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Databricks, Spark, PySpark, Informatica PowerCenter, Oracle, Data Modeling, ETL, ELT, Pentaho</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5be313cc3b61a58</t>
+          <t>https://www.indeed.com/viewjob?jk=f58c8be3a69d599b</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>New York City Department of Sanitation</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Informatica PowerCenter, Oracle, Data Modeling, ETL, ELT, Pentaho</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f58c8be3a69d599b</t>
+          <t>https://www.indeed.com/viewjob?jk=d54d860c68542f20</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>IT Software Engineer II</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>Yusen Logistics</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d54d860c68542f20</t>
+          <t>https://www.indeed.com/viewjob?jk=d97e3542d74962da</t>
         </is>
       </c>
     </row>
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d97e3542d74962da</t>
+          <t>https://www.indeed.com/viewjob?jk=ef2fe730515dbece</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>IT Software Engineer II</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Yusen Logistics</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins</t>
+          <t>Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef2fe730515dbece</t>
+          <t>https://www.indeed.com/viewjob?jk=ac0b8be0e4857da6</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr Data Scientist - Member Growth &amp; Prescreen Modeling</t>
+          <t>Developer Operations Engineer I</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>Transcor Data Services</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Tukwila, WA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Snowflake, MLOps</t>
+          <t>AWS, RDS, Azure, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93bbd48d3322e5c7</t>
+          <t>https://www.indeed.com/viewjob?jk=b84e13a37c8822b9</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Sr Data Scientist - Member Growth &amp; Prescreen Modeling</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Tukwila, WA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac0b8be0e4857da6</t>
+          <t>https://www.indeed.com/viewjob?jk=93bbd48d3322e5c7</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Developer Operations Engineer I</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Transcor Data Services</t>
+          <t>Univision Communications Inc</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, IAM, Google Cloud Platform, GCP, Hadoop, Spark, Scala, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b84e13a37c8822b9</t>
+          <t>https://www.indeed.com/viewjob?jk=b2f885fbfd483879</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Platform Software Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Univision Communications Inc</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, IAM, Google Cloud Platform, GCP, Hadoop, Spark, Scala, dbt, CI/CD, Terraform</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, CI/CD, Kubernetes, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2f885fbfd483879</t>
+          <t>https://www.indeed.com/viewjob?jk=a25c9133cd0e70a2</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Platform Software Engineer</t>
+          <t>Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>El Pollo Loco</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, CI/CD, Kubernetes, Airflow, Apache Airflow, Git</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, SQL Server, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a25c9133cd0e70a2</t>
+          <t>https://www.indeed.com/viewjob?jk=8bd72bf197f82e23</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer</t>
+          <t>Senior Software Engineer - SRE Focus</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>El Pollo Loco</t>
+          <t>CNH Industrial</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Sioux Falls, SD, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, SQL Server, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, MongoDB, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bd72bf197f82e23</t>
+          <t>https://www.indeed.com/viewjob?jk=d07053a0ea5ac768</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - SRE Focus</t>
+          <t>Senior Data Engineer - Orchestration</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>CNH Industrial</t>
+          <t>Arvest Bank</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, MongoDB, ELT, CI/CD, Terraform</t>
+          <t>AWS, RDS, GCP, Dataflow, Scala, Kafka, ETL, dbt, Tableau, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d07053a0ea5ac768</t>
+          <t>https://www.indeed.com/viewjob?jk=e8fe7267b8b9de10</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Orchestration</t>
+          <t>Data Engineer, League Analytics &amp; Infrastructure</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Arvest Bank</t>
+          <t>Major League Baseball</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Dataflow, Scala, Kafka, ETL, dbt, Tableau, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,19 +2841,19 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8fe7267b8b9de10</t>
+          <t>https://www.indeed.com/viewjob?jk=5e63e2ea97ff196b</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer, League Analytics &amp; Infrastructure</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Major League Baseball</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2866,17 +2866,17 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, dbt, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e63e2ea97ff196b</t>
+          <t>https://www.indeed.com/viewjob?jk=90ffeeb2227958d7</t>
         </is>
       </c>
     </row>
@@ -3023,25 +3023,25 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Big Data Software Engineer - Remote</t>
+          <t>Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Ulta</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a57c804e0f6cdd8d</t>
+          <t>https://www.indeed.com/viewjob?jk=371cb08487cb7590</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior AI Software Engineer</t>
+          <t>Senior Big Data Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Bosch</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Plymouth, MI, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Scala, MLOps, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f03c5058699b33f7</t>
+          <t>https://www.indeed.com/viewjob?jk=a57c804e0f6cdd8d</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Junior Analytics Engineer</t>
+          <t>Senior AI Software Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SewerAI</t>
+          <t>Bosch</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Walnut Creek, CA, US USA</t>
+          <t>Plymouth, MI, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, BigQuery, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Scala, MLOps, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef23c8da578678cc</t>
+          <t>https://www.indeed.com/viewjob?jk=f03c5058699b33f7</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Engineer - 2 Openings</t>
+          <t>Junior Analytics Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Blood Cancer United</t>
+          <t>SewerAI</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Walnut Creek, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Blob Storage, GCP, Scala, Snowflake, Data Modeling, Kimball</t>
+          <t>AWS, Redshift, S3, IAM, RDS, BigQuery, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd9f154e39bab643</t>
+          <t>https://www.indeed.com/viewjob?jk=ef23c8da578678cc</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Python AI Engineer</t>
+          <t>Data Engineer - 2 Openings</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Blood Cancer United</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Kafka, PostgreSQL, ETL, CI/CD, Jenkins, Maven, Docker, Jenkins, pytest, Airflow</t>
+          <t>AWS, S3, RDS, Azure, Blob Storage, GCP, Scala, Snowflake, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=277d01c969e4d645</t>
+          <t>https://www.indeed.com/viewjob?jk=dd9f154e39bab643</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Sr BI Analyst</t>
+          <t>Python AI Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Mizkan America</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,17 +3216,17 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Dataflow, Spark, PySpark, Scala, Data Modeling, Power BI, CI/CD</t>
+          <t>Kafka, PostgreSQL, ETL, CI/CD, Jenkins, Maven, Docker, Jenkins, pytest, Airflow</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4207b3535cb26a9b</t>
+          <t>https://www.indeed.com/viewjob?jk=277d01c969e4d645</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Wausau, WI, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Kafka, Snowflake, Oracle, ETL, CI/CD, Jenkins, Jenkins, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2a4a5c971b6dae8</t>
+          <t>https://www.indeed.com/viewjob?jk=276c91b178e50bc3</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Software Engineer, Enterprise Software</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, NoSQL, Splunk, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=276c91b178e50bc3</t>
+          <t>https://www.indeed.com/viewjob?jk=424a613517dace69</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Enterprise Software</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Wausau, WI, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,69 +3391,69 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, NoSQL, Splunk, Docker, Kubernetes</t>
+          <t>AWS, RDS, Kafka, Snowflake, Oracle, ETL, CI/CD, Jenkins, Jenkins, Airflow</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=424a613517dace69</t>
+          <t>https://www.indeed.com/viewjob?jk=f2a4a5c971b6dae8</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Sr BI Analyst</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Mizkan America</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Docker</t>
+          <t>RDS, Azure, Synapse Analytics, Dataflow, Spark, PySpark, Scala, Data Modeling, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d930f40a8264fcae</t>
+          <t>https://www.indeed.com/viewjob?jk=4207b3535cb26a9b</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>MuleSoft QA Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ec42b333047dabf</t>
+          <t>https://www.indeed.com/viewjob?jk=d930f40a8264fcae</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Sustainability Data and AI Consultant</t>
+          <t>MuleSoft QA Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Git, Python</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc927e4fc5649b27</t>
+          <t>https://www.indeed.com/viewjob?jk=8ec42b333047dabf</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Software Engineer ll, Data Platform</t>
+          <t>Site Reliability Engineer III</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Cohere Health</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,17 +3531,17 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, EMR, Athena, S3, RDS, Scala, Kafka, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Splunk, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80e694b601457a09</t>
+          <t>https://www.indeed.com/viewjob?jk=08f29a39eb33f231</t>
         </is>
       </c>
     </row>
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7976a31d4fb905fe</t>
+          <t>https://www.indeed.com/viewjob?jk=bc927e4fc5649b27</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer ll, Data Platform</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Cohere Health</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Lake Buena Vista, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, S3, Databricks, Kafka, Snowflake, PostgreSQL, Data Modeling, Docker, Kubernetes, Airflow</t>
+          <t>AWS, EMR, Athena, S3, RDS, Scala, Kafka, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0309d0101fc2195f</t>
+          <t>https://www.indeed.com/viewjob?jk=80e694b601457a09</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Sustainability Data and AI Consultant</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Git, Python</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04b2fdcc099c4491</t>
+          <t>https://www.indeed.com/viewjob?jk=7976a31d4fb905fe</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>AI Engineer III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Visual Comfort &amp; Co</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Lake Buena Vista, FL, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI, Python</t>
+          <t>AWS, S3, Databricks, Kafka, Snowflake, PostgreSQL, Data Modeling, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed6f23c724c8deb1</t>
+          <t>https://www.indeed.com/viewjob?jk=0309d0101fc2195f</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>MuleSoft Developer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, Oracle, SQL Server, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2aedb694782bdb77</t>
+          <t>https://www.indeed.com/viewjob?jk=04b2fdcc099c4491</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Digital Services Engineer</t>
+          <t>AI Engineer III</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Continental</t>
+          <t>Visual Comfort &amp; Co</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Clinton, MD, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, NoSQL, Docker, Kubernetes, Git, Python</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92b28fa10f3665b6</t>
+          <t>https://www.indeed.com/viewjob?jk=ed6f23c724c8deb1</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>MuleSoft Developer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Blaine, MN, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, Oracle, SQL Server, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=171a3405a6bf87d5</t>
+          <t>https://www.indeed.com/viewjob?jk=2aedb694782bdb77</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>AI Systems Engineer</t>
+          <t>Digital Services Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Continental</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Clinton, MD, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, Databricks, Scala, Kafka, Databricks Lakehouse, NoSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, NoSQL, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c00f3c6eabf7aab0</t>
+          <t>https://www.indeed.com/viewjob?jk=92b28fa10f3665b6</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Software Engineering Supervisor - Hybrid</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Sunrise Banks</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Blaine, MN, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, NoSQL, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=853197679fd8570c</t>
+          <t>https://www.indeed.com/viewjob?jk=171a3405a6bf87d5</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Python/Agentic AI</t>
+          <t>AI Systems Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>BlackLine</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Kafka, PostgreSQL, NoSQL, Docker</t>
+          <t>AWS, SQS, SNS, IAM, RDS, Databricks, Scala, Kafka, Databricks Lakehouse, NoSQL</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f2ba4e75ec79621</t>
+          <t>https://www.indeed.com/viewjob?jk=c00f3c6eabf7aab0</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Security Platform Engineer 2 (Hybrid - Seattle)</t>
+          <t>Software Engineering Supervisor - Hybrid</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Sunrise Banks</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,15 +3916,85 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, NoSQL, CI/CD, Azure DevOps, Git</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=853197679fd8570c</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Python/Agentic AI</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>BlackLine</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Pleasanton, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Kafka, PostgreSQL, NoSQL, Docker</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2f2ba4e75ec79621</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Security Platform Engineer 2 (Hybrid - Seattle)</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Nordstrom</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=49744f4cb7f46ca9</t>
         </is>

--- a/results/job_matches_2026-06-27.xlsx
+++ b/results/job_matches_2026-06-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G102"/>
+  <dimension ref="A1:G104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -853,17 +853,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Quant Analytics Associate Sr - DART</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Networking for Future, Inc.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,52 +871,52 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, ETL, ELT, dbt, Tableau</t>
+          <t>AWS, Step Functions, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=958563c6ca41d7c8</t>
+          <t>https://www.indeed.com/viewjob?jk=0b36615465054406</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Quant Analytics Associate Sr - DART</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Athena, IAM, RDS, Databricks, Scala, Snowflake, ETL</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, ETL, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feff26b7bae36907</t>
+          <t>https://www.indeed.com/viewjob?jk=958563c6ca41d7c8</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=694cbe94ae40ae5b</t>
+          <t>https://www.indeed.com/viewjob?jk=feff26b7bae36907</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0f4bf7cb698e418</t>
+          <t>https://www.indeed.com/viewjob?jk=694cbe94ae40ae5b</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48492fee574585c7</t>
+          <t>https://www.indeed.com/viewjob?jk=a0f4bf7cb698e418</t>
         </is>
       </c>
     </row>
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a3e9b920b8a4519</t>
+          <t>https://www.indeed.com/viewjob?jk=48492fee574585c7</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Architect – Washington, DC</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Creative Information Technology India</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Falls Church, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL</t>
+          <t>AWS, Lambda, Kinesis, Athena, IAM, RDS, Databricks, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94d5786e7c110147</t>
+          <t>https://www.indeed.com/viewjob?jk=6a3e9b920b8a4519</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr. IT Big Data Developer</t>
+          <t>Data Architect – Washington, DC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Diverse Agile Solutions</t>
+          <t>Creative Information Technology India</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Falls Church, VA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1121,64 +1121,64 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dba4bfa4195a614f</t>
+          <t>https://www.indeed.com/viewjob?jk=94d5786e7c110147</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior IT Big Data Developer</t>
+          <t>Sr. IT Big Data Developer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Centurion Consulting Group</t>
+          <t>Diverse Agile Solutions</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, Step Functions, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae26c12caca27959</t>
+          <t>https://www.indeed.com/viewjob?jk=dba4bfa4195a614f</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer Senior - Big Data Platform Team</t>
+          <t>Senior IT Big Data Developer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Centurion Consulting Group</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Farmers Branch, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Spark, Scala, Data Modeling, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bd359ddd135794e</t>
+          <t>https://www.indeed.com/viewjob?jk=ae26c12caca27959</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer Senior - Big Data Platform Team</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>retail services &amp; systems</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Farmers Branch, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake, Dimensional Modeling, ETL</t>
+          <t>S3, RDS, Azure, Spark, Scala, Data Modeling, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f105ffde2d1f4df</t>
+          <t>https://www.indeed.com/viewjob?jk=0bd359ddd135794e</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior IT Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Centurion Consulting Group</t>
+          <t>retail services &amp; systems</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>RDS, Databricks, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efb360d7f7dedcd5</t>
+          <t>https://www.indeed.com/viewjob?jk=0f105ffde2d1f4df</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Platform</t>
+          <t>Senior IT Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Centurion Consulting Group</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ecc89ba914fc587</t>
+          <t>https://www.indeed.com/viewjob?jk=efb360d7f7dedcd5</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Enterprise Data Services</t>
+          <t>Senior Software Engineer - Platform</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Wellmark Blue Cross and Blue Shield</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, RDS</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96ed3a70f59cd7a0</t>
+          <t>https://www.indeed.com/viewjob?jk=3ecc89ba914fc587</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer III (US)</t>
+          <t>Senior Software Engineer - Enterprise Data Services</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>Wellmark Blue Cross and Blue Shield</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Google Cloud Platform, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, RDS</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3f872ac99e6bd1a</t>
+          <t>https://www.indeed.com/viewjob?jk=96ed3a70f59cd7a0</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Architect (173743)</t>
+          <t>Software Engineer III (US)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, Scala, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Google Cloud Platform, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9545b3f6e705f68</t>
+          <t>https://www.indeed.com/viewjob?jk=d3f872ac99e6bd1a</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Consultant- Data/AI Due Diligence-MTS</t>
+          <t>Data Architect (173743)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b6bc1ec4cda3c8e</t>
+          <t>https://www.indeed.com/viewjob?jk=c9545b3f6e705f68</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Engineer, Invest Tech</t>
+          <t>Senior BI Developer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>Foundation Building Materials</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, Dataflow, Spark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efdcc6d0c28ecda9</t>
+          <t>https://www.indeed.com/viewjob?jk=25c1cd979546661c</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Consultant- Data/AI Due Diligence-MTS</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Energy Services Group</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22692d347007686c</t>
+          <t>https://www.indeed.com/viewjob?jk=7b6bc1ec4cda3c8e</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=418fe6804d9bbee5</t>
+          <t>https://www.indeed.com/viewjob?jk=efdcc6d0c28ecda9</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Engineer, Invest Tech</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>Energy Services Group</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=455cbc0d06bec7dd</t>
+          <t>https://www.indeed.com/viewjob?jk=22692d347007686c</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>Senior Engineer, Invest Tech</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=861d82e3c9e267af</t>
+          <t>https://www.indeed.com/viewjob?jk=418fe6804d9bbee5</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Engineer, Invest Tech</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32c289c0954d3b83</t>
+          <t>https://www.indeed.com/viewjob?jk=455cbc0d06bec7dd</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=563ad203b5a2853e</t>
+          <t>https://www.indeed.com/viewjob?jk=861d82e3c9e267af</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c88857b2990a629</t>
+          <t>https://www.indeed.com/viewjob?jk=32c289c0954d3b83</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c30d6189ed53ff4</t>
+          <t>https://www.indeed.com/viewjob?jk=563ad203b5a2853e</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9f1090e8d875682</t>
+          <t>https://www.indeed.com/viewjob?jk=9c88857b2990a629</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09009f7e617a8382</t>
+          <t>https://www.indeed.com/viewjob?jk=6c30d6189ed53ff4</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3c113a0ea31c0ed</t>
+          <t>https://www.indeed.com/viewjob?jk=c9f1090e8d875682</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5962eb966972f6e</t>
+          <t>https://www.indeed.com/viewjob?jk=09009f7e617a8382</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Full Stack</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69e822c1cf66e308</t>
+          <t>https://www.indeed.com/viewjob?jk=b3c113a0ea31c0ed</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Full Stack</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37dbcc8bf6973335</t>
+          <t>https://www.indeed.com/viewjob?jk=d5962eb966972f6e</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d84fecedb12dd363</t>
+          <t>https://www.indeed.com/viewjob?jk=69e822c1cf66e308</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abe999fc3b54fcb4</t>
+          <t>https://www.indeed.com/viewjob?jk=37dbcc8bf6973335</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer 2 - Full Stack</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b49f50dbf2988c82</t>
+          <t>https://www.indeed.com/viewjob?jk=d84fecedb12dd363</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer 2 - Full Stack</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,17 +2096,17 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d75b791cf50c1184</t>
+          <t>https://www.indeed.com/viewjob?jk=abe999fc3b54fcb4</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=776060619ca92d8b</t>
+          <t>https://www.indeed.com/viewjob?jk=b49f50dbf2988c82</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2362abd894783c27</t>
+          <t>https://www.indeed.com/viewjob?jk=d75b791cf50c1184</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,94 +2211,94 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=992a2c5f94075440</t>
+          <t>https://www.indeed.com/viewjob?jk=776060619ca92d8b</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Engineering</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Fubo</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e24be3cd83341f1</t>
+          <t>https://www.indeed.com/viewjob?jk=2362abd894783c27</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8122e2600ab1407a</t>
+          <t>https://www.indeed.com/viewjob?jk=992a2c5f94075440</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Platform Engineer (Associate)</t>
+          <t>Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>Fubo</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52b81f936f231329</t>
+          <t>https://www.indeed.com/viewjob?jk=0e24be3cd83341f1</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Arc Technologies Group</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ccc63169a66ef59</t>
+          <t>https://www.indeed.com/viewjob?jk=8122e2600ab1407a</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Remote Kubernetes Engineer</t>
+          <t>Data Platform Engineer (Associate)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Cloud Data Vision</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5be313cc3b61a58</t>
+          <t>https://www.indeed.com/viewjob?jk=52b81f936f231329</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>New York City Department of Sanitation</t>
+          <t>Arc Technologies Group</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Informatica PowerCenter, Oracle, Data Modeling, ETL, ELT, Pentaho</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f58c8be3a69d599b</t>
+          <t>https://www.indeed.com/viewjob?jk=8ccc63169a66ef59</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Remote Kubernetes Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>Cloud Data Vision</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, Snowflake</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d54d860c68542f20</t>
+          <t>https://www.indeed.com/viewjob?jk=b5be313cc3b61a58</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>IT Software Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Yusen Logistics</t>
+          <t>New York City Department of Sanitation</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins</t>
+          <t>RDS, Databricks, Spark, PySpark, Informatica PowerCenter, Oracle, Data Modeling, ETL, ELT, Pentaho</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d97e3542d74962da</t>
+          <t>https://www.indeed.com/viewjob?jk=f58c8be3a69d599b</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>IT Software Engineer II</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Yusen Logistics</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef2fe730515dbece</t>
+          <t>https://www.indeed.com/viewjob?jk=d54d860c68542f20</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>IT Software Engineer II</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Yusen Logistics</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac0b8be0e4857da6</t>
+          <t>https://www.indeed.com/viewjob?jk=d97e3542d74962da</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Developer Operations Engineer I</t>
+          <t>IT Software Engineer II</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Transcor Data Services</t>
+          <t>Yusen Logistics</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b84e13a37c8822b9</t>
+          <t>https://www.indeed.com/viewjob?jk=ef2fe730515dbece</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr Data Scientist - Member Growth &amp; Prescreen Modeling</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Tukwila, WA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Snowflake, MLOps</t>
+          <t>Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93bbd48d3322e5c7</t>
+          <t>https://www.indeed.com/viewjob?jk=ac0b8be0e4857da6</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Developer Operations Engineer I</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Univision Communications Inc</t>
+          <t>Transcor Data Services</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, IAM, Google Cloud Platform, GCP, Hadoop, Spark, Scala, dbt, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2f885fbfd483879</t>
+          <t>https://www.indeed.com/viewjob?jk=b84e13a37c8822b9</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Platform Software Engineer</t>
+          <t>Sr Data Scientist - Member Growth &amp; Prescreen Modeling</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Tukwila, WA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, CI/CD, Kubernetes, Airflow, Apache Airflow, Git</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a25c9133cd0e70a2</t>
+          <t>https://www.indeed.com/viewjob?jk=93bbd48d3322e5c7</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>El Pollo Loco</t>
+          <t>Univision Communications Inc</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, SQL Server, DynamoDB, CI/CD</t>
+          <t>AWS, IAM, Google Cloud Platform, GCP, Hadoop, Spark, Scala, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bd72bf197f82e23</t>
+          <t>https://www.indeed.com/viewjob?jk=b2f885fbfd483879</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - SRE Focus</t>
+          <t>Data Platform Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CNH Industrial</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, MongoDB, ELT, CI/CD, Terraform</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, CI/CD, Kubernetes, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d07053a0ea5ac768</t>
+          <t>https://www.indeed.com/viewjob?jk=a25c9133cd0e70a2</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Orchestration</t>
+          <t>Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Arvest Bank</t>
+          <t>El Pollo Loco</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Dataflow, Scala, Kafka, ETL, dbt, Tableau, Docker</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, SQL Server, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8fe7267b8b9de10</t>
+          <t>https://www.indeed.com/viewjob?jk=8bd72bf197f82e23</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer, League Analytics &amp; Infrastructure</t>
+          <t>Senior Software Engineer - SRE Focus</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Major League Baseball</t>
+          <t>CNH Industrial</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Sioux Falls, SD, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, MongoDB, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e63e2ea97ff196b</t>
+          <t>https://www.indeed.com/viewjob?jk=d07053a0ea5ac768</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Engineer - Orchestration</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Arvest Bank</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, GCP, Dataflow, Scala, Kafka, ETL, dbt, Tableau, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90ffeeb2227958d7</t>
+          <t>https://www.indeed.com/viewjob?jk=e8fe7267b8b9de10</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Hybrid</t>
+          <t>Data Engineer, League Analytics &amp; Infrastructure</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Major League Baseball</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Google Cloud Platform, GCP</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c3e33c47a701cd2</t>
+          <t>https://www.indeed.com/viewjob?jk=5e63e2ea97ff196b</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Hybrid</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Google Cloud Platform, GCP</t>
+          <t>AWS, S3, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e620dabe0cd123</t>
+          <t>https://www.indeed.com/viewjob?jk=90ffeeb2227958d7</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Senior Software Engineer - Hybrid</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Ameriprise Financial</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Dataflow, Oracle, SQL Server, PostgreSQL, ETL, MLOps</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Google Cloud Platform, GCP</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dc316693a524ae7</t>
+          <t>https://www.indeed.com/viewjob?jk=6c3e33c47a701cd2</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Software Engineer | Middleware</t>
+          <t>Senior Software Engineer - Hybrid</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ExtraHop Networks</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, IAM, RDS, Azure, GCP, Scala, PostgreSQL, Terraform</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Google Cloud Platform, GCP</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=111ecbafdd773723</t>
+          <t>https://www.indeed.com/viewjob?jk=03e620dabe0cd123</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Cloud Security Engineer</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Ulta</t>
+          <t>Ameriprise Financial</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Dataflow, Oracle, SQL Server, PostgreSQL, ETL, MLOps</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=371cb08487cb7590</t>
+          <t>https://www.indeed.com/viewjob?jk=2dc316693a524ae7</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Big Data Software Engineer - Remote</t>
+          <t>Senior Software Engineer | Middleware</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>ExtraHop Networks</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, S3, SQS, IAM, RDS, Azure, GCP, Scala, PostgreSQL, Terraform</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a57c804e0f6cdd8d</t>
+          <t>https://www.indeed.com/viewjob?jk=111ecbafdd773723</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior AI Software Engineer</t>
+          <t>Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Bosch</t>
+          <t>Ulta</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Plymouth, MI, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Scala, MLOps, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f03c5058699b33f7</t>
+          <t>https://www.indeed.com/viewjob?jk=371cb08487cb7590</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Junior Analytics Engineer</t>
+          <t>Senior Big Data Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SewerAI</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Walnut Creek, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, BigQuery, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef23c8da578678cc</t>
+          <t>https://www.indeed.com/viewjob?jk=a57c804e0f6cdd8d</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer - 2 Openings</t>
+          <t>Senior AI Software Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Blood Cancer United</t>
+          <t>Bosch</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plymouth, MI, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Blob Storage, GCP, Scala, Snowflake, Data Modeling, Kimball</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Scala, MLOps, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd9f154e39bab643</t>
+          <t>https://www.indeed.com/viewjob?jk=f03c5058699b33f7</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Python AI Engineer</t>
+          <t>Junior Analytics Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>SewerAI</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Walnut Creek, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Kafka, PostgreSQL, ETL, CI/CD, Jenkins, Maven, Docker, Jenkins, pytest, Airflow</t>
+          <t>AWS, Redshift, S3, IAM, RDS, BigQuery, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=277d01c969e4d645</t>
+          <t>https://www.indeed.com/viewjob?jk=ef23c8da578678cc</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Sr RPA Process Automation Developer (UIPATH)</t>
+          <t>Data Engineer - 2 Openings</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>Blood Cancer United</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, S3, RDS, Azure, Blob Storage, GCP, Scala, Snowflake, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23d1d78d2eac45da</t>
+          <t>https://www.indeed.com/viewjob?jk=dd9f154e39bab643</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior .net Software Engineer</t>
+          <t>Python AI Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Azure, Spark, Scala, SQL Server, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>Kafka, PostgreSQL, ETL, CI/CD, Jenkins, Maven, Docker, Jenkins, pytest, Airflow</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ec84c14bbe42215</t>
+          <t>https://www.indeed.com/viewjob?jk=277d01c969e4d645</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr RPA Process Automation Developer (UIPATH)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=276c91b178e50bc3</t>
+          <t>https://www.indeed.com/viewjob?jk=23d1d78d2eac45da</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Enterprise Software</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, NoSQL, Splunk, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=424a613517dace69</t>
+          <t>https://www.indeed.com/viewjob?jk=276c91b178e50bc3</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior .net Software Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Wausau, WI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Kafka, Snowflake, Oracle, ETL, CI/CD, Jenkins, Jenkins, Airflow</t>
+          <t>Azure, Spark, Scala, SQL Server, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2a4a5c971b6dae8</t>
+          <t>https://www.indeed.com/viewjob?jk=2ec84c14bbe42215</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Sr BI Analyst</t>
+          <t>Sr. Software Engineer, Enterprise Software</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Mizkan America</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Dataflow, Spark, PySpark, Scala, Data Modeling, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, NoSQL, Splunk, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4207b3535cb26a9b</t>
+          <t>https://www.indeed.com/viewjob?jk=424a613517dace69</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Wausau, WI, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Docker</t>
+          <t>AWS, RDS, Kafka, Snowflake, Oracle, ETL, CI/CD, Jenkins, Jenkins, Airflow</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,59 +3471,59 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d930f40a8264fcae</t>
+          <t>https://www.indeed.com/viewjob?jk=f2a4a5c971b6dae8</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>MuleSoft QA Engineer</t>
+          <t>Sr BI Analyst</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>Mizkan America</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Synapse Analytics, Dataflow, Spark, PySpark, Scala, Data Modeling, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ec42b333047dabf</t>
+          <t>https://www.indeed.com/viewjob?jk=4207b3535cb26a9b</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Splunk, Kubernetes, Datadog</t>
+          <t>AWS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08f29a39eb33f231</t>
+          <t>https://www.indeed.com/viewjob?jk=d930f40a8264fcae</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Sustainability Data and AI Consultant</t>
+          <t>MuleSoft QA Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Git, Python</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc927e4fc5649b27</t>
+          <t>https://www.indeed.com/viewjob?jk=8ec42b333047dabf</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Software Engineer ll, Data Platform</t>
+          <t>Site Reliability Engineer III</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Cohere Health</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,17 +3601,17 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, EMR, Athena, S3, RDS, Scala, Kafka, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Splunk, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80e694b601457a09</t>
+          <t>https://www.indeed.com/viewjob?jk=08f29a39eb33f231</t>
         </is>
       </c>
     </row>
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7976a31d4fb905fe</t>
+          <t>https://www.indeed.com/viewjob?jk=bc927e4fc5649b27</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer ll, Data Platform</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Cohere Health</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Lake Buena Vista, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, S3, Databricks, Kafka, Snowflake, PostgreSQL, Data Modeling, Docker, Kubernetes, Airflow</t>
+          <t>AWS, EMR, Athena, S3, RDS, Scala, Kafka, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0309d0101fc2195f</t>
+          <t>https://www.indeed.com/viewjob?jk=80e694b601457a09</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Sustainability Data and AI Consultant</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Git, Python</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04b2fdcc099c4491</t>
+          <t>https://www.indeed.com/viewjob?jk=7976a31d4fb905fe</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>AI Engineer III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Visual Comfort &amp; Co</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Lake Buena Vista, FL, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI, Python</t>
+          <t>AWS, S3, Databricks, Kafka, Snowflake, PostgreSQL, Data Modeling, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed6f23c724c8deb1</t>
+          <t>https://www.indeed.com/viewjob?jk=0309d0101fc2195f</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>MuleSoft Developer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, Oracle, SQL Server, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2aedb694782bdb77</t>
+          <t>https://www.indeed.com/viewjob?jk=04b2fdcc099c4491</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Digital Services Engineer</t>
+          <t>AI Engineer III</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Continental</t>
+          <t>Visual Comfort &amp; Co</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Clinton, MD, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, NoSQL, Docker, Kubernetes, Git, Python</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92b28fa10f3665b6</t>
+          <t>https://www.indeed.com/viewjob?jk=ed6f23c724c8deb1</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>MuleSoft Developer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Blaine, MN, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, Oracle, SQL Server, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=171a3405a6bf87d5</t>
+          <t>https://www.indeed.com/viewjob?jk=2aedb694782bdb77</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>AI Systems Engineer</t>
+          <t>Digital Services Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Continental</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Clinton, MD, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, Databricks, Scala, Kafka, Databricks Lakehouse, NoSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, NoSQL, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c00f3c6eabf7aab0</t>
+          <t>https://www.indeed.com/viewjob?jk=92b28fa10f3665b6</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Software Engineering Supervisor - Hybrid</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Sunrise Banks</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Blaine, MN, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, NoSQL, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=853197679fd8570c</t>
+          <t>https://www.indeed.com/viewjob?jk=171a3405a6bf87d5</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Python/Agentic AI</t>
+          <t>AI Systems Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>BlackLine</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Kafka, PostgreSQL, NoSQL, Docker</t>
+          <t>AWS, SQS, SNS, IAM, RDS, Databricks, Scala, Kafka, Databricks Lakehouse, NoSQL</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f2ba4e75ec79621</t>
+          <t>https://www.indeed.com/viewjob?jk=c00f3c6eabf7aab0</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Security Platform Engineer 2 (Hybrid - Seattle)</t>
+          <t>Software Engineering Supervisor - Hybrid</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Sunrise Banks</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,15 +3986,85 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, NoSQL, CI/CD, Azure DevOps, Git</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=853197679fd8570c</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Python/Agentic AI</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>BlackLine</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Pleasanton, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Kafka, PostgreSQL, NoSQL, Docker</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2f2ba4e75ec79621</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Security Platform Engineer 2 (Hybrid - Seattle)</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Nordstrom</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=49744f4cb7f46ca9</t>
         </is>

--- a/results/job_matches_2026-06-27.xlsx
+++ b/results/job_matches_2026-06-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G104"/>
+  <dimension ref="A1:G103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -853,17 +853,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Quant Analytics Associate Sr - DART</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Networking for Future, Inc.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, ETL, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b36615465054406</t>
+          <t>https://www.indeed.com/viewjob?jk=958563c6ca41d7c8</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Quant Analytics Associate Sr - DART</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Networking for Future, Inc.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,17 +906,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, ETL, ELT, dbt, Tableau</t>
+          <t>AWS, Step Functions, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=958563c6ca41d7c8</t>
+          <t>https://www.indeed.com/viewjob?jk=0b36615465054406</t>
         </is>
       </c>
     </row>
@@ -1413,17 +1413,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Architect (173743)</t>
+          <t>Senior BI Developer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Foundation Building Materials</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, Scala, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, Dataflow, Spark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9545b3f6e705f68</t>
+          <t>https://www.indeed.com/viewjob?jk=25c1cd979546661c</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior BI Developer</t>
+          <t>Data Architect (173743)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Foundation Building Materials</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, Dataflow, Spark, Scala, SQL Server</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25c1cd979546661c</t>
+          <t>https://www.indeed.com/viewjob?jk=c9545b3f6e705f68</t>
         </is>
       </c>
     </row>
@@ -3723,17 +3723,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Lake Buena Vista, FL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, S3, Databricks, Kafka, Snowflake, PostgreSQL, Data Modeling, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0309d0101fc2195f</t>
+          <t>https://www.indeed.com/viewjob?jk=04b2fdcc099c4491</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>AI Engineer III</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Visual Comfort &amp; Co</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04b2fdcc099c4491</t>
+          <t>https://www.indeed.com/viewjob?jk=ed6f23c724c8deb1</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>AI Engineer III</t>
+          <t>MuleSoft Developer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Visual Comfort &amp; Co</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI, Python</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, Oracle, SQL Server, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed6f23c724c8deb1</t>
+          <t>https://www.indeed.com/viewjob?jk=2aedb694782bdb77</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>MuleSoft Developer</t>
+          <t>Digital Services Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>Continental</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Clinton, MD, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, Oracle, SQL Server, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, NoSQL, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2aedb694782bdb77</t>
+          <t>https://www.indeed.com/viewjob?jk=92b28fa10f3665b6</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Digital Services Engineer</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Continental</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Clinton, MD, US USA</t>
+          <t>Blaine, MN, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, NoSQL, Docker, Kubernetes, Git, Python</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92b28fa10f3665b6</t>
+          <t>https://www.indeed.com/viewjob?jk=171a3405a6bf87d5</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>AI Systems Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Blaine, MN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, SQS, SNS, IAM, RDS, Databricks, Scala, Kafka, Databricks Lakehouse, NoSQL</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=171a3405a6bf87d5</t>
+          <t>https://www.indeed.com/viewjob?jk=c00f3c6eabf7aab0</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>AI Systems Engineer</t>
+          <t>Software Engineering Supervisor - Hybrid</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Sunrise Banks</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, Databricks, Scala, Kafka, Databricks Lakehouse, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, NoSQL, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c00f3c6eabf7aab0</t>
+          <t>https://www.indeed.com/viewjob?jk=853197679fd8570c</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Software Engineering Supervisor - Hybrid</t>
+          <t>Senior Software Engineer - Python/Agentic AI</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Sunrise Banks</t>
+          <t>BlackLine</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, NoSQL, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Kafka, PostgreSQL, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=853197679fd8570c</t>
+          <t>https://www.indeed.com/viewjob?jk=2f2ba4e75ec79621</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Python/Agentic AI</t>
+          <t>Security Platform Engineer 2 (Hybrid - Seattle)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>BlackLine</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Kafka, PostgreSQL, NoSQL, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4030,41 +4030,6 @@
         </is>
       </c>
       <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2f2ba4e75ec79621</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Security Platform Engineer 2 (Hybrid - Seattle)</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Nordstrom</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=49744f4cb7f46ca9</t>
         </is>

--- a/results/job_matches_2026-06-27.xlsx
+++ b/results/job_matches_2026-06-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G103"/>
+  <dimension ref="A1:G101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,52 +538,52 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer C1</t>
+          <t>Data Engineer (Business Analyst IV)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Fairfax County Government</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Scala, Kafka</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, BigQuery, Cloud Storage, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=797ab0abe77eeb1d</t>
+          <t>https://www.indeed.com/viewjob?jk=414e38f5ca1fe7f7</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer C1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Edwards Lifesciences</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02a96598db050be0</t>
+          <t>https://www.indeed.com/viewjob?jk=797ab0abe77eeb1d</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Data</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Edwards Lifesciences</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0631739ce734e7c7</t>
+          <t>https://www.indeed.com/viewjob?jk=02a96598db050be0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing</t>
+          <t>Engineer/Sr Engineer, IT Data</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,14 +671,14 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2158d7493af1e09e</t>
+          <t>https://www.indeed.com/viewjob?jk=0631739ce734e7c7</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr. Specialist Solutions Architect - Data Engineering &amp; Warehousing</t>
+          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35b4bec9ddbc42a3</t>
+          <t>https://www.indeed.com/viewjob?jk=2158d7493af1e09e</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Sr. Specialist Solutions Architect - Data Engineering &amp; Warehousing</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>WSSC Water</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Laurel, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Blob Storage, GCP, Hadoop</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efacd6764e780443</t>
+          <t>https://www.indeed.com/viewjob?jk=35b4bec9ddbc42a3</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior API Cloud Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Transflo</t>
+          <t>WSSC Water</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Laurel, MD, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Blob Storage, GCP, Hadoop</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,19 +776,19 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6877ccbd8db8810</t>
+          <t>https://www.indeed.com/viewjob?jk=efacd6764e780443</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Mainframe Analyst (Healthcare)</t>
+          <t>Senior API Cloud Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NSV IT SOLUTIONS</t>
+          <t>Transflo</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,59 +811,59 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=529186dc1f0e5461</t>
+          <t>https://www.indeed.com/viewjob?jk=c6877ccbd8db8810</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior IT Data Engineer</t>
+          <t>Mainframe Analyst (Healthcare)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Diverse Agile Solutions</t>
+          <t>NSV IT SOLUTIONS</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=445f550d4f69a7c6</t>
+          <t>https://www.indeed.com/viewjob?jk=529186dc1f0e5461</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Quant Analytics Associate Sr - DART</t>
+          <t>Senior IT Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Diverse Agile Solutions</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,17 +871,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, ETL, ELT, dbt, Tableau</t>
+          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=958563c6ca41d7c8</t>
+          <t>https://www.indeed.com/viewjob?jk=445f550d4f69a7c6</t>
         </is>
       </c>
     </row>
@@ -923,35 +923,35 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Quant Analytics Associate Sr - DART</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Athena, IAM, RDS, Databricks, Scala, Snowflake, ETL</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, ETL, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feff26b7bae36907</t>
+          <t>https://www.indeed.com/viewjob?jk=958563c6ca41d7c8</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=694cbe94ae40ae5b</t>
+          <t>https://www.indeed.com/viewjob?jk=feff26b7bae36907</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0f4bf7cb698e418</t>
+          <t>https://www.indeed.com/viewjob?jk=694cbe94ae40ae5b</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48492fee574585c7</t>
+          <t>https://www.indeed.com/viewjob?jk=a0f4bf7cb698e418</t>
         </is>
       </c>
     </row>
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a3e9b920b8a4519</t>
+          <t>https://www.indeed.com/viewjob?jk=48492fee574585c7</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Architect – Washington, DC</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Creative Information Technology India</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Falls Church, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL</t>
+          <t>AWS, Lambda, Kinesis, Athena, IAM, RDS, Databricks, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94d5786e7c110147</t>
+          <t>https://www.indeed.com/viewjob?jk=6a3e9b920b8a4519</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr. IT Big Data Developer</t>
+          <t>Data Architect – Washington, DC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Diverse Agile Solutions</t>
+          <t>Creative Information Technology India</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Falls Church, VA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1156,64 +1156,64 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dba4bfa4195a614f</t>
+          <t>https://www.indeed.com/viewjob?jk=94d5786e7c110147</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior IT Big Data Developer</t>
+          <t>Sr. IT Big Data Developer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Centurion Consulting Group</t>
+          <t>Diverse Agile Solutions</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, Step Functions, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae26c12caca27959</t>
+          <t>https://www.indeed.com/viewjob?jk=dba4bfa4195a614f</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer Senior - Big Data Platform Team</t>
+          <t>Senior IT Big Data Developer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Centurion Consulting Group</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Farmers Branch, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Spark, Scala, Data Modeling, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bd359ddd135794e</t>
+          <t>https://www.indeed.com/viewjob?jk=ae26c12caca27959</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer Senior - Big Data Platform Team</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>retail services &amp; systems</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Farmers Branch, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake, Dimensional Modeling, ETL</t>
+          <t>S3, RDS, Azure, Spark, Scala, Data Modeling, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f105ffde2d1f4df</t>
+          <t>https://www.indeed.com/viewjob?jk=0bd359ddd135794e</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior IT Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Centurion Consulting Group</t>
+          <t>retail services &amp; systems</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>RDS, Databricks, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efb360d7f7dedcd5</t>
+          <t>https://www.indeed.com/viewjob?jk=0f105ffde2d1f4df</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Platform</t>
+          <t>Senior IT Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Centurion Consulting Group</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ecc89ba914fc587</t>
+          <t>https://www.indeed.com/viewjob?jk=efb360d7f7dedcd5</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Enterprise Data Services</t>
+          <t>Senior Software Engineer - Platform</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Wellmark Blue Cross and Blue Shield</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, RDS</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96ed3a70f59cd7a0</t>
+          <t>https://www.indeed.com/viewjob?jk=3ecc89ba914fc587</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer III (US)</t>
+          <t>Senior Software Engineer - Enterprise Data Services</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>Wellmark Blue Cross and Blue Shield</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Google Cloud Platform, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, RDS</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3f872ac99e6bd1a</t>
+          <t>https://www.indeed.com/viewjob?jk=96ed3a70f59cd7a0</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior BI Developer</t>
+          <t>Software Engineer III (US)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Foundation Building Materials</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, Dataflow, Spark, Scala, SQL Server</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Google Cloud Platform, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25c1cd979546661c</t>
+          <t>https://www.indeed.com/viewjob?jk=d3f872ac99e6bd1a</t>
         </is>
       </c>
     </row>
@@ -1483,17 +1483,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Consultant- Data/AI Due Diligence-MTS</t>
+          <t>Senior BI Developer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>Foundation Building Materials</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, Dataflow, Spark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b6bc1ec4cda3c8e</t>
+          <t>https://www.indeed.com/viewjob?jk=25c1cd979546661c</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Engineer, Invest Tech</t>
+          <t>Senior Consultant- Data/AI Due Diligence-MTS</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efdcc6d0c28ecda9</t>
+          <t>https://www.indeed.com/viewjob?jk=7b6bc1ec4cda3c8e</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Engineer, Invest Tech</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Energy Services Group</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22692d347007686c</t>
+          <t>https://www.indeed.com/viewjob?jk=efdcc6d0c28ecda9</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Engineer, Invest Tech</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>Energy Services Group</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=418fe6804d9bbee5</t>
+          <t>https://www.indeed.com/viewjob?jk=22692d347007686c</t>
         </is>
       </c>
     </row>
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=455cbc0d06bec7dd</t>
+          <t>https://www.indeed.com/viewjob?jk=418fe6804d9bbee5</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>Senior Engineer, Invest Tech</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=861d82e3c9e267af</t>
+          <t>https://www.indeed.com/viewjob?jk=455cbc0d06bec7dd</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32c289c0954d3b83</t>
+          <t>https://www.indeed.com/viewjob?jk=861d82e3c9e267af</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=563ad203b5a2853e</t>
+          <t>https://www.indeed.com/viewjob?jk=32c289c0954d3b83</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c88857b2990a629</t>
+          <t>https://www.indeed.com/viewjob?jk=563ad203b5a2853e</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c30d6189ed53ff4</t>
+          <t>https://www.indeed.com/viewjob?jk=9c88857b2990a629</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9f1090e8d875682</t>
+          <t>https://www.indeed.com/viewjob?jk=6c30d6189ed53ff4</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09009f7e617a8382</t>
+          <t>https://www.indeed.com/viewjob?jk=c9f1090e8d875682</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3c113a0ea31c0ed</t>
+          <t>https://www.indeed.com/viewjob?jk=09009f7e617a8382</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5962eb966972f6e</t>
+          <t>https://www.indeed.com/viewjob?jk=b3c113a0ea31c0ed</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Full Stack</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69e822c1cf66e308</t>
+          <t>https://www.indeed.com/viewjob?jk=d5962eb966972f6e</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37dbcc8bf6973335</t>
+          <t>https://www.indeed.com/viewjob?jk=69e822c1cf66e308</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d84fecedb12dd363</t>
+          <t>https://www.indeed.com/viewjob?jk=37dbcc8bf6973335</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abe999fc3b54fcb4</t>
+          <t>https://www.indeed.com/viewjob?jk=d84fecedb12dd363</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer 2 - Full Stack</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,17 +2131,17 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b49f50dbf2988c82</t>
+          <t>https://www.indeed.com/viewjob?jk=abe999fc3b54fcb4</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d75b791cf50c1184</t>
+          <t>https://www.indeed.com/viewjob?jk=b49f50dbf2988c82</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=776060619ca92d8b</t>
+          <t>https://www.indeed.com/viewjob?jk=d75b791cf50c1184</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2362abd894783c27</t>
+          <t>https://www.indeed.com/viewjob?jk=776060619ca92d8b</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,59 +2281,59 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=992a2c5f94075440</t>
+          <t>https://www.indeed.com/viewjob?jk=2362abd894783c27</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Engineering</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Fubo</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e24be3cd83341f1</t>
+          <t>https://www.indeed.com/viewjob?jk=992a2c5f94075440</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Fubo</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8122e2600ab1407a</t>
+          <t>https://www.indeed.com/viewjob?jk=0e24be3cd83341f1</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Platform Engineer (Associate)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52b81f936f231329</t>
+          <t>https://www.indeed.com/viewjob?jk=8122e2600ab1407a</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Data Platform Engineer (Associate)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Arc Technologies Group</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ccc63169a66ef59</t>
+          <t>https://www.indeed.com/viewjob?jk=52b81f936f231329</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Remote Kubernetes Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Cloud Data Vision</t>
+          <t>Arc Technologies Group</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5be313cc3b61a58</t>
+          <t>https://www.indeed.com/viewjob?jk=8ccc63169a66ef59</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Remote Kubernetes Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>New York City Department of Sanitation</t>
+          <t>Cloud Data Vision</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Informatica PowerCenter, Oracle, Data Modeling, ETL, ELT, Pentaho</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f58c8be3a69d599b</t>
+          <t>https://www.indeed.com/viewjob?jk=b5be313cc3b61a58</t>
         </is>
       </c>
     </row>
@@ -2813,17 +2813,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - SRE Focus</t>
+          <t>Senior Data Engineer - Orchestration</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>CNH Industrial</t>
+          <t>Arvest Bank</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, MongoDB, ELT, CI/CD, Terraform</t>
+          <t>AWS, RDS, GCP, Dataflow, Scala, Kafka, ETL, dbt, Tableau, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d07053a0ea5ac768</t>
+          <t>https://www.indeed.com/viewjob?jk=e8fe7267b8b9de10</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Orchestration</t>
+          <t>Data Engineer, League Analytics &amp; Infrastructure</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Arvest Bank</t>
+          <t>Major League Baseball</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Dataflow, Scala, Kafka, ETL, dbt, Tableau, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,19 +2876,19 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8fe7267b8b9de10</t>
+          <t>https://www.indeed.com/viewjob?jk=5e63e2ea97ff196b</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer, League Analytics &amp; Infrastructure</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Major League Baseball</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, dbt, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e63e2ea97ff196b</t>
+          <t>https://www.indeed.com/viewjob?jk=90ffeeb2227958d7</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Software Engineer - Hybrid</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,17 +2936,17 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Google Cloud Platform, GCP</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90ffeeb2227958d7</t>
+          <t>https://www.indeed.com/viewjob?jk=6c3e33c47a701cd2</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c3e33c47a701cd2</t>
+          <t>https://www.indeed.com/viewjob?jk=03e620dabe0cd123</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Hybrid</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Ameriprise Financial</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Google Cloud Platform, GCP</t>
+          <t>AWS, RDS, Azure, GCP, Dataflow, Oracle, SQL Server, PostgreSQL, ETL, MLOps</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e620dabe0cd123</t>
+          <t>https://www.indeed.com/viewjob?jk=2dc316693a524ae7</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Senior Software Engineer | Middleware</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Ameriprise Financial</t>
+          <t>ExtraHop Networks</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Dataflow, Oracle, SQL Server, PostgreSQL, ETL, MLOps</t>
+          <t>AWS, S3, SQS, IAM, RDS, Azure, GCP, Scala, PostgreSQL, Terraform</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dc316693a524ae7</t>
+          <t>https://www.indeed.com/viewjob?jk=111ecbafdd773723</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Software Engineer | Middleware</t>
+          <t>Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>ExtraHop Networks</t>
+          <t>Ulta</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, IAM, RDS, Azure, GCP, Scala, PostgreSQL, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=111ecbafdd773723</t>
+          <t>https://www.indeed.com/viewjob?jk=371cb08487cb7590</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Cloud Security Engineer</t>
+          <t>Senior Big Data Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Ulta</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=371cb08487cb7590</t>
+          <t>https://www.indeed.com/viewjob?jk=a57c804e0f6cdd8d</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Big Data Software Engineer - Remote</t>
+          <t>Senior AI Software Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Bosch</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Plymouth, MI, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Scala, MLOps, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a57c804e0f6cdd8d</t>
+          <t>https://www.indeed.com/viewjob?jk=f03c5058699b33f7</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior AI Software Engineer</t>
+          <t>Junior Analytics Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Bosch</t>
+          <t>SewerAI</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Plymouth, MI, US USA</t>
+          <t>Walnut Creek, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Scala, MLOps, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, Redshift, S3, IAM, RDS, BigQuery, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f03c5058699b33f7</t>
+          <t>https://www.indeed.com/viewjob?jk=ef23c8da578678cc</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Junior Analytics Engineer</t>
+          <t>Data Engineer - 2 Openings</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SewerAI</t>
+          <t>Blood Cancer United</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Walnut Creek, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, BigQuery, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, S3, RDS, Azure, Blob Storage, GCP, Scala, Snowflake, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef23c8da578678cc</t>
+          <t>https://www.indeed.com/viewjob?jk=dd9f154e39bab643</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Engineer - 2 Openings</t>
+          <t>Python AI Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Blood Cancer United</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Blob Storage, GCP, Scala, Snowflake, Data Modeling, Kimball</t>
+          <t>Kafka, PostgreSQL, ETL, CI/CD, Jenkins, Maven, Docker, Jenkins, pytest, Airflow</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd9f154e39bab643</t>
+          <t>https://www.indeed.com/viewjob?jk=277d01c969e4d645</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Python AI Engineer</t>
+          <t>Sr RPA Process Automation Developer (UIPATH)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Kafka, PostgreSQL, ETL, CI/CD, Jenkins, Maven, Docker, Jenkins, pytest, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=277d01c969e4d645</t>
+          <t>https://www.indeed.com/viewjob?jk=23d1d78d2eac45da</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sr RPA Process Automation Developer (UIPATH)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Wausau, WI, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, RDS, Kafka, Snowflake, Oracle, ETL, CI/CD, Jenkins, Jenkins, Airflow</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23d1d78d2eac45da</t>
+          <t>https://www.indeed.com/viewjob?jk=f2a4a5c971b6dae8</t>
         </is>
       </c>
     </row>
@@ -3408,17 +3408,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Enterprise Software</t>
+          <t>Sr BI Analyst</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Mizkan America</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, NoSQL, Splunk, Docker, Kubernetes</t>
+          <t>RDS, Azure, Synapse Analytics, Dataflow, Spark, PySpark, Scala, Data Modeling, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=424a613517dace69</t>
+          <t>https://www.indeed.com/viewjob?jk=4207b3535cb26a9b</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Wausau, WI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Kafka, Snowflake, Oracle, ETL, CI/CD, Jenkins, Jenkins, Airflow</t>
+          <t>AWS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,59 +3471,59 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2a4a5c971b6dae8</t>
+          <t>https://www.indeed.com/viewjob?jk=d930f40a8264fcae</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Sr BI Analyst</t>
+          <t>MuleSoft QA Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Mizkan America</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Dataflow, Spark, PySpark, Scala, Data Modeling, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4207b3535cb26a9b</t>
+          <t>https://www.indeed.com/viewjob?jk=8ec42b333047dabf</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Site Reliability Engineer III</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Docker</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Splunk, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d930f40a8264fcae</t>
+          <t>https://www.indeed.com/viewjob?jk=08f29a39eb33f231</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>MuleSoft QA Engineer</t>
+          <t>Sustainability Data and AI Consultant</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Git, Python</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ec42b333047dabf</t>
+          <t>https://www.indeed.com/viewjob?jk=bc927e4fc5649b27</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III</t>
+          <t>Software Engineer ll, Data Platform</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Cohere Health</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,17 +3601,17 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Splunk, Kubernetes, Datadog</t>
+          <t>AWS, EMR, Athena, S3, RDS, Scala, Kafka, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08f29a39eb33f231</t>
+          <t>https://www.indeed.com/viewjob?jk=80e694b601457a09</t>
         </is>
       </c>
     </row>
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc927e4fc5649b27</t>
+          <t>https://www.indeed.com/viewjob?jk=7976a31d4fb905fe</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Software Engineer ll, Data Platform</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Cohere Health</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, EMR, Athena, S3, RDS, Scala, Kafka, dbt, CI/CD, Airflow</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80e694b601457a09</t>
+          <t>https://www.indeed.com/viewjob?jk=04b2fdcc099c4491</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Sustainability Data and AI Consultant</t>
+          <t>AI Engineer III</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Visual Comfort &amp; Co</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Git, Python</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7976a31d4fb905fe</t>
+          <t>https://www.indeed.com/viewjob?jk=ed6f23c724c8deb1</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>MuleSoft Developer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, Oracle, SQL Server, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04b2fdcc099c4491</t>
+          <t>https://www.indeed.com/viewjob?jk=2aedb694782bdb77</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>AI Engineer III</t>
+          <t>Digital Services Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Visual Comfort &amp; Co</t>
+          <t>Continental</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Clinton, MD, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI, Python</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, NoSQL, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed6f23c724c8deb1</t>
+          <t>https://www.indeed.com/viewjob?jk=92b28fa10f3665b6</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>MuleSoft Developer</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Blaine, MN, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, Oracle, SQL Server, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2aedb694782bdb77</t>
+          <t>https://www.indeed.com/viewjob?jk=171a3405a6bf87d5</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Digital Services Engineer</t>
+          <t>AI Systems Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Continental</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Clinton, MD, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, NoSQL, Docker, Kubernetes, Git, Python</t>
+          <t>AWS, SQS, SNS, IAM, RDS, Databricks, Scala, Kafka, Databricks Lakehouse, NoSQL</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92b28fa10f3665b6</t>
+          <t>https://www.indeed.com/viewjob?jk=c00f3c6eabf7aab0</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>Software Engineering Supervisor - Hybrid</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Sunrise Banks</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Blaine, MN, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, NoSQL, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=171a3405a6bf87d5</t>
+          <t>https://www.indeed.com/viewjob?jk=853197679fd8570c</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>AI Systems Engineer</t>
+          <t>Senior Software Engineer - Python/Agentic AI</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>BlackLine</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, IAM, RDS, Databricks, Scala, Kafka, Databricks Lakehouse, NoSQL</t>
+          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Kafka, PostgreSQL, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c00f3c6eabf7aab0</t>
+          <t>https://www.indeed.com/viewjob?jk=2f2ba4e75ec79621</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Software Engineering Supervisor - Hybrid</t>
+          <t>Security Platform Engineer 2 (Hybrid - Seattle)</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Sunrise Banks</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, NoSQL, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3960,76 +3960,6 @@
         </is>
       </c>
       <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=853197679fd8570c</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Python/Agentic AI</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>BlackLine</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Pleasanton, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Kafka, PostgreSQL, NoSQL, Docker</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2f2ba4e75ec79621</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Security Platform Engineer 2 (Hybrid - Seattle)</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Nordstrom</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=49744f4cb7f46ca9</t>
         </is>

--- a/results/job_matches_2026-06-27.xlsx
+++ b/results/job_matches_2026-06-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G101"/>
+  <dimension ref="A1:G92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>Resmed</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.5</v>
+        <v>20.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Azure, GCP, BigQuery</t>
+          <t>AWS, Kinesis, RDS, Databricks, Spark, Scala, Kafka, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,94 +496,94 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8b8b3a8aa7e371a</t>
+          <t>https://www.indeed.com/viewjob?jk=db8f881d56beb45b</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Engineering</t>
+          <t>Data Engineer (Business Analyst IV)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Resmed</t>
+          <t>Fairfax County Government</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.8</v>
+        <v>18.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Spark, Scala, Kafka, Snowflake, SQL Server, PostgreSQL</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, BigQuery, Cloud Storage, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db8f881d56beb45b</t>
+          <t>https://www.indeed.com/viewjob?jk=414e38f5ca1fe7f7</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer (Business Analyst IV)</t>
+          <t>Data Engineer C1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Fairfax County Government</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, BigQuery, Cloud Storage, Hadoop, Spark, Scala</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=414e38f5ca1fe7f7</t>
+          <t>https://www.indeed.com/viewjob?jk=797ab0abe77eeb1d</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer C1</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Edwards Lifesciences</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=797ab0abe77eeb1d</t>
+          <t>https://www.indeed.com/viewjob?jk=02a96598db050be0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer/Sr Engineer, IT Data</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Edwards Lifesciences</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02a96598db050be0</t>
+          <t>https://www.indeed.com/viewjob?jk=0631739ce734e7c7</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Data</t>
+          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,14 +671,14 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0631739ce734e7c7</t>
+          <t>https://www.indeed.com/viewjob?jk=2158d7493af1e09e</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing</t>
+          <t>Sr. Specialist Solutions Architect - Data Engineering &amp; Warehousing</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2158d7493af1e09e</t>
+          <t>https://www.indeed.com/viewjob?jk=35b4bec9ddbc42a3</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. Specialist Solutions Architect - Data Engineering &amp; Warehousing</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>WSSC Water</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Laurel, MD, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Blob Storage, GCP, Hadoop</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35b4bec9ddbc42a3</t>
+          <t>https://www.indeed.com/viewjob?jk=efacd6764e780443</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior API Cloud Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>WSSC Water</t>
+          <t>Transflo</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Laurel, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Blob Storage, GCP, Hadoop</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,19 +776,19 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efacd6764e780443</t>
+          <t>https://www.indeed.com/viewjob?jk=c6877ccbd8db8810</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior API Cloud Engineer</t>
+          <t>Mainframe Analyst (Healthcare)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Transflo</t>
+          <t>NSV IT SOLUTIONS</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,59 +811,59 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6877ccbd8db8810</t>
+          <t>https://www.indeed.com/viewjob?jk=529186dc1f0e5461</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Mainframe Analyst (Healthcare)</t>
+          <t>Senior IT Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NSV IT SOLUTIONS</t>
+          <t>Diverse Agile Solutions</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=529186dc1f0e5461</t>
+          <t>https://www.indeed.com/viewjob?jk=445f550d4f69a7c6</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior IT Data Engineer</t>
+          <t>Quant Analytics Associate Sr - DART</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Diverse Agile Solutions</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,17 +871,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, ETL, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=445f550d4f69a7c6</t>
+          <t>https://www.indeed.com/viewjob?jk=958563c6ca41d7c8</t>
         </is>
       </c>
     </row>
@@ -923,35 +923,35 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Quant Analytics Associate Sr - DART</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, ETL, ELT, dbt, Tableau</t>
+          <t>AWS, Lambda, Kinesis, Athena, IAM, RDS, Databricks, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=958563c6ca41d7c8</t>
+          <t>https://www.indeed.com/viewjob?jk=feff26b7bae36907</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feff26b7bae36907</t>
+          <t>https://www.indeed.com/viewjob?jk=694cbe94ae40ae5b</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=694cbe94ae40ae5b</t>
+          <t>https://www.indeed.com/viewjob?jk=a0f4bf7cb698e418</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0f4bf7cb698e418</t>
+          <t>https://www.indeed.com/viewjob?jk=48492fee574585c7</t>
         </is>
       </c>
     </row>
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48492fee574585c7</t>
+          <t>https://www.indeed.com/viewjob?jk=6a3e9b920b8a4519</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Architect – Washington, DC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Creative Information Technology India</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Falls Church, VA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Athena, IAM, RDS, Databricks, Scala, Snowflake, ETL</t>
+          <t>AWS, Step Functions, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a3e9b920b8a4519</t>
+          <t>https://www.indeed.com/viewjob?jk=94d5786e7c110147</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Architect – Washington, DC</t>
+          <t>Sr. IT Big Data Developer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Creative Information Technology India</t>
+          <t>Diverse Agile Solutions</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Falls Church, VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1156,64 +1156,64 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94d5786e7c110147</t>
+          <t>https://www.indeed.com/viewjob?jk=dba4bfa4195a614f</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr. IT Big Data Developer</t>
+          <t>Senior IT Big Data Developer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Diverse Agile Solutions</t>
+          <t>Centurion Consulting Group</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL</t>
+          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dba4bfa4195a614f</t>
+          <t>https://www.indeed.com/viewjob?jk=ae26c12caca27959</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior IT Big Data Developer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Centurion Consulting Group</t>
+          <t>retail services &amp; systems</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>RDS, Databricks, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae26c12caca27959</t>
+          <t>https://www.indeed.com/viewjob?jk=0f105ffde2d1f4df</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer Senior - Big Data Platform Team</t>
+          <t>Senior IT Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Centurion Consulting Group</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Farmers Branch, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Spark, Scala, Data Modeling, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bd359ddd135794e</t>
+          <t>https://www.indeed.com/viewjob?jk=efb360d7f7dedcd5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Software Engineer - Platform</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>retail services &amp; systems</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f105ffde2d1f4df</t>
+          <t>https://www.indeed.com/viewjob?jk=3ecc89ba914fc587</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior IT Data Engineer</t>
+          <t>Software Engineer III (US)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Centurion Consulting Group</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Google Cloud Platform, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efb360d7f7dedcd5</t>
+          <t>https://www.indeed.com/viewjob?jk=d3f872ac99e6bd1a</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Platform</t>
+          <t>Senior BI Developer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Foundation Building Materials</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, Dataflow, Spark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ecc89ba914fc587</t>
+          <t>https://www.indeed.com/viewjob?jk=25c1cd979546661c</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Enterprise Data Services</t>
+          <t>Data Architect (173743)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Wellmark Blue Cross and Blue Shield</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, RDS</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96ed3a70f59cd7a0</t>
+          <t>https://www.indeed.com/viewjob?jk=c9545b3f6e705f68</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer III (US)</t>
+          <t>Senior Consultant- Data/AI Due Diligence-MTS</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Google Cloud Platform, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3f872ac99e6bd1a</t>
+          <t>https://www.indeed.com/viewjob?jk=7b6bc1ec4cda3c8e</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Architect (173743)</t>
+          <t>Senior Engineer, Invest Tech</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, Scala, Snowflake, Oracle</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9545b3f6e705f68</t>
+          <t>https://www.indeed.com/viewjob?jk=efdcc6d0c28ecda9</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior BI Developer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Foundation Building Materials</t>
+          <t>Energy Services Group</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, Dataflow, Spark, Scala, SQL Server</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25c1cd979546661c</t>
+          <t>https://www.indeed.com/viewjob?jk=22692d347007686c</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Consultant- Data/AI Due Diligence-MTS</t>
+          <t>Senior Engineer, Invest Tech</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b6bc1ec4cda3c8e</t>
+          <t>https://www.indeed.com/viewjob?jk=418fe6804d9bbee5</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efdcc6d0c28ecda9</t>
+          <t>https://www.indeed.com/viewjob?jk=455cbc0d06bec7dd</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Energy Services Group</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22692d347007686c</t>
+          <t>https://www.indeed.com/viewjob?jk=861d82e3c9e267af</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Engineer, Invest Tech</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=418fe6804d9bbee5</t>
+          <t>https://www.indeed.com/viewjob?jk=32c289c0954d3b83</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Engineer, Invest Tech</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=455cbc0d06bec7dd</t>
+          <t>https://www.indeed.com/viewjob?jk=563ad203b5a2853e</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=861d82e3c9e267af</t>
+          <t>https://www.indeed.com/viewjob?jk=9c88857b2990a629</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32c289c0954d3b83</t>
+          <t>https://www.indeed.com/viewjob?jk=6c30d6189ed53ff4</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=563ad203b5a2853e</t>
+          <t>https://www.indeed.com/viewjob?jk=c9f1090e8d875682</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c88857b2990a629</t>
+          <t>https://www.indeed.com/viewjob?jk=09009f7e617a8382</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c30d6189ed53ff4</t>
+          <t>https://www.indeed.com/viewjob?jk=b3c113a0ea31c0ed</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9f1090e8d875682</t>
+          <t>https://www.indeed.com/viewjob?jk=d5962eb966972f6e</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Software Engineer 2 - Full Stack</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09009f7e617a8382</t>
+          <t>https://www.indeed.com/viewjob?jk=69e822c1cf66e308</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Software Engineer 2 - Full Stack</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3c113a0ea31c0ed</t>
+          <t>https://www.indeed.com/viewjob?jk=37dbcc8bf6973335</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Software Engineer 2 - Full Stack</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5962eb966972f6e</t>
+          <t>https://www.indeed.com/viewjob?jk=d84fecedb12dd363</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69e822c1cf66e308</t>
+          <t>https://www.indeed.com/viewjob?jk=abe999fc3b54fcb4</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Full Stack</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37dbcc8bf6973335</t>
+          <t>https://www.indeed.com/viewjob?jk=b49f50dbf2988c82</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Full Stack</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d84fecedb12dd363</t>
+          <t>https://www.indeed.com/viewjob?jk=d75b791cf50c1184</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Full Stack</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,17 +2131,17 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abe999fc3b54fcb4</t>
+          <t>https://www.indeed.com/viewjob?jk=776060619ca92d8b</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b49f50dbf2988c82</t>
+          <t>https://www.indeed.com/viewjob?jk=2362abd894783c27</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,129 +2211,129 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d75b791cf50c1184</t>
+          <t>https://www.indeed.com/viewjob?jk=992a2c5f94075440</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Fubo</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=776060619ca92d8b</t>
+          <t>https://www.indeed.com/viewjob?jk=0e24be3cd83341f1</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2362abd894783c27</t>
+          <t>https://www.indeed.com/viewjob?jk=8122e2600ab1407a</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Platform Engineer (Associate)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=992a2c5f94075440</t>
+          <t>https://www.indeed.com/viewjob?jk=52b81f936f231329</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Engineering</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Fubo</t>
+          <t>Arc Technologies Group</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e24be3cd83341f1</t>
+          <t>https://www.indeed.com/viewjob?jk=8ccc63169a66ef59</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>IT Software Engineer II</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Yusen Logistics</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8122e2600ab1407a</t>
+          <t>https://www.indeed.com/viewjob?jk=d97e3542d74962da</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Platform Engineer (Associate)</t>
+          <t>IT Software Engineer II</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>Yusen Logistics</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52b81f936f231329</t>
+          <t>https://www.indeed.com/viewjob?jk=ef2fe730515dbece</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Arc Technologies Group</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ccc63169a66ef59</t>
+          <t>https://www.indeed.com/viewjob?jk=ac0b8be0e4857da6</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Remote Kubernetes Engineer</t>
+          <t>Developer Operations Engineer I</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Cloud Data Vision</t>
+          <t>Transcor Data Services</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5be313cc3b61a58</t>
+          <t>https://www.indeed.com/viewjob?jk=b84e13a37c8822b9</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Sr Data Scientist - Member Growth &amp; Prescreen Modeling</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Tukwila, WA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d54d860c68542f20</t>
+          <t>https://www.indeed.com/viewjob?jk=93bbd48d3322e5c7</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>IT Software Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Yusen Logistics</t>
+          <t>Univision Communications Inc</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, IAM, Google Cloud Platform, GCP, Hadoop, Spark, Scala, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d97e3542d74962da</t>
+          <t>https://www.indeed.com/viewjob?jk=b2f885fbfd483879</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>IT Software Engineer II</t>
+          <t>Data Platform Software Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Yusen Logistics</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, CI/CD, Kubernetes, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef2fe730515dbece</t>
+          <t>https://www.indeed.com/viewjob?jk=a25c9133cd0e70a2</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>El Pollo Loco</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, SQL Server, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac0b8be0e4857da6</t>
+          <t>https://www.indeed.com/viewjob?jk=8bd72bf197f82e23</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Developer Operations Engineer I</t>
+          <t>Senior Data Engineer - Orchestration</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Transcor Data Services</t>
+          <t>Arvest Bank</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, GCP, Dataflow, Scala, Kafka, ETL, dbt, Tableau, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b84e13a37c8822b9</t>
+          <t>https://www.indeed.com/viewjob?jk=e8fe7267b8b9de10</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr Data Scientist - Member Growth &amp; Prescreen Modeling</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Tukwila, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Snowflake, MLOps</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, S3, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93bbd48d3322e5c7</t>
+          <t>https://www.indeed.com/viewjob?jk=9d2302c7e6b6aaf2</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Univision Communications Inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, IAM, Google Cloud Platform, GCP, Hadoop, Spark, Scala, dbt, CI/CD, Terraform</t>
+          <t>AWS, S3, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2f885fbfd483879</t>
+          <t>https://www.indeed.com/viewjob?jk=90ffeeb2227958d7</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Platform Software Engineer</t>
+          <t>Senior Software Engineer - Hybrid</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, CI/CD, Kubernetes, Airflow, Apache Airflow, Git</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Google Cloud Platform, GCP</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a25c9133cd0e70a2</t>
+          <t>https://www.indeed.com/viewjob?jk=6c3e33c47a701cd2</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer</t>
+          <t>Senior Software Engineer - Hybrid</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>El Pollo Loco</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, SQL Server, DynamoDB, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Google Cloud Platform, GCP</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bd72bf197f82e23</t>
+          <t>https://www.indeed.com/viewjob?jk=03e620dabe0cd123</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Orchestration</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Arvest Bank</t>
+          <t>Ameriprise Financial</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Dataflow, Scala, Kafka, ETL, dbt, Tableau, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Dataflow, Oracle, SQL Server, PostgreSQL, ETL, MLOps</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8fe7267b8b9de10</t>
+          <t>https://www.indeed.com/viewjob?jk=2dc316693a524ae7</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer, League Analytics &amp; Infrastructure</t>
+          <t>Senior Software Engineer | Middleware</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Major League Baseball</t>
+          <t>ExtraHop Networks</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, dbt, CI/CD</t>
+          <t>AWS, S3, SQS, IAM, RDS, Azure, GCP, Scala, PostgreSQL, Terraform</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e63e2ea97ff196b</t>
+          <t>https://www.indeed.com/viewjob?jk=111ecbafdd773723</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ulta</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,42 +2901,42 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90ffeeb2227958d7</t>
+          <t>https://www.indeed.com/viewjob?jk=371cb08487cb7590</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Hybrid</t>
+          <t>Senior Big Data Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Google Cloud Platform, GCP</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c3e33c47a701cd2</t>
+          <t>https://www.indeed.com/viewjob?jk=a57c804e0f6cdd8d</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Hybrid</t>
+          <t>Junior Analytics Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>SewerAI</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Walnut Creek, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Google Cloud Platform, GCP</t>
+          <t>AWS, Redshift, S3, IAM, RDS, BigQuery, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e620dabe0cd123</t>
+          <t>https://www.indeed.com/viewjob?jk=ef23c8da578678cc</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Data Engineer - 2 Openings</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Ameriprise Financial</t>
+          <t>Blood Cancer United</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Dataflow, Oracle, SQL Server, PostgreSQL, ETL, MLOps</t>
+          <t>AWS, S3, RDS, Azure, Blob Storage, GCP, Scala, Snowflake, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dc316693a524ae7</t>
+          <t>https://www.indeed.com/viewjob?jk=dd9f154e39bab643</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Software Engineer | Middleware</t>
+          <t>Python AI Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ExtraHop Networks</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, IAM, RDS, Azure, GCP, Scala, PostgreSQL, Terraform</t>
+          <t>Kafka, PostgreSQL, ETL, CI/CD, Jenkins, Maven, Docker, Jenkins, pytest, Airflow</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=111ecbafdd773723</t>
+          <t>https://www.indeed.com/viewjob?jk=277d01c969e4d645</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Cloud Security Engineer</t>
+          <t>Data Bricks Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Ulta</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=371cb08487cb7590</t>
+          <t>https://www.indeed.com/viewjob?jk=834e54031f069664</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Big Data Software Engineer - Remote</t>
+          <t>Sr RPA Process Automation Developer (UIPATH)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a57c804e0f6cdd8d</t>
+          <t>https://www.indeed.com/viewjob?jk=23d1d78d2eac45da</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior AI Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Bosch</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Plymouth, MI, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Scala, MLOps, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f03c5058699b33f7</t>
+          <t>https://www.indeed.com/viewjob?jk=276c91b178e50bc3</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Junior Analytics Engineer</t>
+          <t>Sr BI Analyst</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SewerAI</t>
+          <t>Mizkan America</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Walnut Creek, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,42 +3181,42 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, BigQuery, Snowflake, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Synapse Analytics, Dataflow, Spark, PySpark, Scala, Data Modeling, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef23c8da578678cc</t>
+          <t>https://www.indeed.com/viewjob?jk=4207b3535cb26a9b</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Engineer - 2 Openings</t>
+          <t>MuleSoft QA Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Blood Cancer United</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Blob Storage, GCP, Scala, Snowflake, Data Modeling, Kimball</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,67 +3226,67 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd9f154e39bab643</t>
+          <t>https://www.indeed.com/viewjob?jk=8ec42b333047dabf</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Python AI Engineer</t>
+          <t>Site Reliability Engineer III</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Kafka, PostgreSQL, ETL, CI/CD, Jenkins, Maven, Docker, Jenkins, pytest, Airflow</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Splunk, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=277d01c969e4d645</t>
+          <t>https://www.indeed.com/viewjob?jk=08f29a39eb33f231</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sr RPA Process Automation Developer (UIPATH)</t>
+          <t>Sustainability Data and AI Consultant</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Git, Python</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23d1d78d2eac45da</t>
+          <t>https://www.indeed.com/viewjob?jk=bc927e4fc5649b27</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer ll, Data Platform</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Cohere Health</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Wausau, WI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Kafka, Snowflake, Oracle, ETL, CI/CD, Jenkins, Jenkins, Airflow</t>
+          <t>AWS, EMR, Athena, S3, RDS, Scala, Kafka, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2a4a5c971b6dae8</t>
+          <t>https://www.indeed.com/viewjob?jk=80e694b601457a09</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sustainability Data and AI Consultant</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Git, Python</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=276c91b178e50bc3</t>
+          <t>https://www.indeed.com/viewjob?jk=7976a31d4fb905fe</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior .net Software Engineer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Azure, Spark, Scala, SQL Server, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,59 +3401,59 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ec84c14bbe42215</t>
+          <t>https://www.indeed.com/viewjob?jk=04b2fdcc099c4491</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Sr BI Analyst</t>
+          <t>AI Engineer III</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Mizkan America</t>
+          <t>Visual Comfort &amp; Co</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Dataflow, Spark, PySpark, Scala, Data Modeling, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4207b3535cb26a9b</t>
+          <t>https://www.indeed.com/viewjob?jk=ed6f23c724c8deb1</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>MuleSoft Developer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, Oracle, SQL Server, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d930f40a8264fcae</t>
+          <t>https://www.indeed.com/viewjob?jk=2aedb694782bdb77</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>MuleSoft QA Engineer</t>
+          <t>Digital Services Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>Continental</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Clinton, MD, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, NoSQL, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ec42b333047dabf</t>
+          <t>https://www.indeed.com/viewjob?jk=92b28fa10f3665b6</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Blaine, MN, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Splunk, Kubernetes, Datadog</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08f29a39eb33f231</t>
+          <t>https://www.indeed.com/viewjob?jk=171a3405a6bf87d5</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Sustainability Data and AI Consultant</t>
+          <t>AI Systems Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Git, Python</t>
+          <t>AWS, SQS, SNS, IAM, RDS, Databricks, Scala, Kafka, Databricks Lakehouse, NoSQL</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc927e4fc5649b27</t>
+          <t>https://www.indeed.com/viewjob?jk=c00f3c6eabf7aab0</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Software Engineer ll, Data Platform</t>
+          <t>Software Engineering Supervisor - Hybrid</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Cohere Health</t>
+          <t>Sunrise Banks</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, EMR, Athena, S3, RDS, Scala, Kafka, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, NoSQL, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80e694b601457a09</t>
+          <t>https://www.indeed.com/viewjob?jk=853197679fd8570c</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Sustainability Data and AI Consultant</t>
+          <t>Security Platform Engineer 2 (Hybrid - Seattle)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3645,321 +3645,6 @@
         </is>
       </c>
       <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7976a31d4fb905fe</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Engineer</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Cognizant</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Eden Prairie, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=04b2fdcc099c4491</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>AI Engineer III</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Visual Comfort &amp; Co</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI, Python</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ed6f23c724c8deb1</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>MuleSoft Developer</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>UniFirst</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Wilmington, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, Oracle, SQL Server, NoSQL, Splunk, CI/CD</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2aedb694782bdb77</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Digital Services Engineer</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Continental</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Clinton, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, NoSQL, Docker, Kubernetes, Git, Python</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=92b28fa10f3665b6</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Snowflake Architect</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Cognizant</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Blaine, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=171a3405a6bf87d5</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>AI Systems Engineer</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Suffolk Construction</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>AWS, SQS, SNS, IAM, RDS, Databricks, Scala, Kafka, Databricks Lakehouse, NoSQL</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c00f3c6eabf7aab0</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Software Engineering Supervisor - Hybrid</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Sunrise Banks</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Saint Paul, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, NoSQL, CI/CD, Azure DevOps, Git</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=853197679fd8570c</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Python/Agentic AI</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>BlackLine</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Pleasanton, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Kafka, PostgreSQL, NoSQL, Docker</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2f2ba4e75ec79621</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Security Platform Engineer 2 (Hybrid - Seattle)</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Nordstrom</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=49744f4cb7f46ca9</t>
         </is>

--- a/results/job_matches_2026-06-27.xlsx
+++ b/results/job_matches_2026-06-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G92"/>
+  <dimension ref="A1:G83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,17 +713,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior API Cloud Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>WSSC Water</t>
+          <t>Transflo</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Laurel, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Blob Storage, GCP, Hadoop</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,19 +741,19 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efacd6764e780443</t>
+          <t>https://www.indeed.com/viewjob?jk=c6877ccbd8db8810</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior API Cloud Engineer</t>
+          <t>Mainframe Analyst (Healthcare)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Transflo</t>
+          <t>NSV IT SOLUTIONS</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,59 +776,59 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6877ccbd8db8810</t>
+          <t>https://www.indeed.com/viewjob?jk=529186dc1f0e5461</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Mainframe Analyst (Healthcare)</t>
+          <t>Senior IT Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NSV IT SOLUTIONS</t>
+          <t>Diverse Agile Solutions</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=529186dc1f0e5461</t>
+          <t>https://www.indeed.com/viewjob?jk=445f550d4f69a7c6</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior IT Data Engineer</t>
+          <t>Quant Analytics Associate Sr - DART</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Diverse Agile Solutions</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, ETL, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=445f550d4f69a7c6</t>
+          <t>https://www.indeed.com/viewjob?jk=958563c6ca41d7c8</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Quant Analytics Associate Sr - DART</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Networking for Future, Inc.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,42 +871,42 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, ETL, ELT, dbt, Tableau</t>
+          <t>AWS, Step Functions, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=958563c6ca41d7c8</t>
+          <t>https://www.indeed.com/viewjob?jk=0b36615465054406</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Networking for Future, Inc.</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL</t>
+          <t>AWS, Lambda, Kinesis, Athena, IAM, RDS, Databricks, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b36615465054406</t>
+          <t>https://www.indeed.com/viewjob?jk=feff26b7bae36907</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feff26b7bae36907</t>
+          <t>https://www.indeed.com/viewjob?jk=694cbe94ae40ae5b</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=694cbe94ae40ae5b</t>
+          <t>https://www.indeed.com/viewjob?jk=a0f4bf7cb698e418</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0f4bf7cb698e418</t>
+          <t>https://www.indeed.com/viewjob?jk=48492fee574585c7</t>
         </is>
       </c>
     </row>
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48492fee574585c7</t>
+          <t>https://www.indeed.com/viewjob?jk=6a3e9b920b8a4519</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Architect – Washington, DC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Creative Information Technology India</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Falls Church, VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Athena, IAM, RDS, Databricks, Scala, Snowflake, ETL</t>
+          <t>AWS, Step Functions, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a3e9b920b8a4519</t>
+          <t>https://www.indeed.com/viewjob?jk=94d5786e7c110147</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Architect – Washington, DC</t>
+          <t>Sr. IT Big Data Developer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Creative Information Technology India</t>
+          <t>Diverse Agile Solutions</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Falls Church, VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1121,64 +1121,64 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94d5786e7c110147</t>
+          <t>https://www.indeed.com/viewjob?jk=dba4bfa4195a614f</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr. IT Big Data Developer</t>
+          <t>Senior IT Big Data Developer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Diverse Agile Solutions</t>
+          <t>Centurion Consulting Group</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL</t>
+          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dba4bfa4195a614f</t>
+          <t>https://www.indeed.com/viewjob?jk=ae26c12caca27959</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior IT Big Data Developer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Centurion Consulting Group</t>
+          <t>retail services &amp; systems</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>RDS, Databricks, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae26c12caca27959</t>
+          <t>https://www.indeed.com/viewjob?jk=0f105ffde2d1f4df</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Software Engineer - Platform</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>retail services &amp; systems</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f105ffde2d1f4df</t>
+          <t>https://www.indeed.com/viewjob?jk=3ecc89ba914fc587</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior IT Data Engineer</t>
+          <t>Senior BI Developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Centurion Consulting Group</t>
+          <t>Foundation Building Materials</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, Dataflow, Spark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efb360d7f7dedcd5</t>
+          <t>https://www.indeed.com/viewjob?jk=25c1cd979546661c</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Platform</t>
+          <t>Data Architect (173743)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ecc89ba914fc587</t>
+          <t>https://www.indeed.com/viewjob?jk=c9545b3f6e705f68</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer III (US)</t>
+          <t>Senior Engineer, Invest Tech</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Google Cloud Platform, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3f872ac99e6bd1a</t>
+          <t>https://www.indeed.com/viewjob?jk=efdcc6d0c28ecda9</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior BI Developer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Foundation Building Materials</t>
+          <t>Energy Services Group</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, Dataflow, Spark, Scala, SQL Server</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25c1cd979546661c</t>
+          <t>https://www.indeed.com/viewjob?jk=22692d347007686c</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Architect (173743)</t>
+          <t>Senior Engineer, Invest Tech</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, Scala, Snowflake, Oracle</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9545b3f6e705f68</t>
+          <t>https://www.indeed.com/viewjob?jk=418fe6804d9bbee5</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Consultant- Data/AI Due Diligence-MTS</t>
+          <t>Senior Engineer, Invest Tech</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b6bc1ec4cda3c8e</t>
+          <t>https://www.indeed.com/viewjob?jk=455cbc0d06bec7dd</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Engineer, Invest Tech</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efdcc6d0c28ecda9</t>
+          <t>https://www.indeed.com/viewjob?jk=861d82e3c9e267af</t>
         </is>
       </c>
     </row>
@@ -1488,7 +1488,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Energy Services Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22692d347007686c</t>
+          <t>https://www.indeed.com/viewjob?jk=32c289c0954d3b83</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Engineer, Invest Tech</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=418fe6804d9bbee5</t>
+          <t>https://www.indeed.com/viewjob?jk=563ad203b5a2853e</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Engineer, Invest Tech</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=455cbc0d06bec7dd</t>
+          <t>https://www.indeed.com/viewjob?jk=9c88857b2990a629</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=861d82e3c9e267af</t>
+          <t>https://www.indeed.com/viewjob?jk=6c30d6189ed53ff4</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32c289c0954d3b83</t>
+          <t>https://www.indeed.com/viewjob?jk=c9f1090e8d875682</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=563ad203b5a2853e</t>
+          <t>https://www.indeed.com/viewjob?jk=09009f7e617a8382</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c88857b2990a629</t>
+          <t>https://www.indeed.com/viewjob?jk=b3c113a0ea31c0ed</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c30d6189ed53ff4</t>
+          <t>https://www.indeed.com/viewjob?jk=d5962eb966972f6e</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Software Engineer 2 - Full Stack</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9f1090e8d875682</t>
+          <t>https://www.indeed.com/viewjob?jk=69e822c1cf66e308</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Software Engineer 2 - Full Stack</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09009f7e617a8382</t>
+          <t>https://www.indeed.com/viewjob?jk=37dbcc8bf6973335</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Software Engineer 2 - Full Stack</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3c113a0ea31c0ed</t>
+          <t>https://www.indeed.com/viewjob?jk=d84fecedb12dd363</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Software Engineer 2 - Full Stack</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5962eb966972f6e</t>
+          <t>https://www.indeed.com/viewjob?jk=abe999fc3b54fcb4</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Full Stack</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69e822c1cf66e308</t>
+          <t>https://www.indeed.com/viewjob?jk=b49f50dbf2988c82</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Full Stack</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37dbcc8bf6973335</t>
+          <t>https://www.indeed.com/viewjob?jk=d75b791cf50c1184</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Full Stack</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d84fecedb12dd363</t>
+          <t>https://www.indeed.com/viewjob?jk=776060619ca92d8b</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Full Stack</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,17 +2026,17 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abe999fc3b54fcb4</t>
+          <t>https://www.indeed.com/viewjob?jk=2362abd894783c27</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,164 +2071,164 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b49f50dbf2988c82</t>
+          <t>https://www.indeed.com/viewjob?jk=992a2c5f94075440</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Fubo</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d75b791cf50c1184</t>
+          <t>https://www.indeed.com/viewjob?jk=0e24be3cd83341f1</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=776060619ca92d8b</t>
+          <t>https://www.indeed.com/viewjob?jk=8122e2600ab1407a</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Platform Engineer (Associate)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2362abd894783c27</t>
+          <t>https://www.indeed.com/viewjob?jk=52b81f936f231329</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>IT Software Engineer II</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Yusen Logistics</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=992a2c5f94075440</t>
+          <t>https://www.indeed.com/viewjob?jk=d97e3542d74962da</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Engineering</t>
+          <t>IT Software Engineer II</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Fubo</t>
+          <t>Yusen Logistics</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e24be3cd83341f1</t>
+          <t>https://www.indeed.com/viewjob?jk=ef2fe730515dbece</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8122e2600ab1407a</t>
+          <t>https://www.indeed.com/viewjob?jk=ac0b8be0e4857da6</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Platform Engineer (Associate)</t>
+          <t>Sr Data Scientist - Member Growth &amp; Prescreen Modeling</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tukwila, WA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52b81f936f231329</t>
+          <t>https://www.indeed.com/viewjob?jk=93bbd48d3322e5c7</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Data Platform Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Arc Technologies Group</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, CI/CD, Kubernetes, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ccc63169a66ef59</t>
+          <t>https://www.indeed.com/viewjob?jk=a25c9133cd0e70a2</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>IT Software Engineer II</t>
+          <t>Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Yusen Logistics</t>
+          <t>El Pollo Loco</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, SQL Server, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d97e3542d74962da</t>
+          <t>https://www.indeed.com/viewjob?jk=8bd72bf197f82e23</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>IT Software Engineer II</t>
+          <t>Senior Data Engineer - Orchestration</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Yusen Logistics</t>
+          <t>Arvest Bank</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, GCP, Dataflow, Scala, Kafka, ETL, dbt, Tableau, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef2fe730515dbece</t>
+          <t>https://www.indeed.com/viewjob?jk=e8fe7267b8b9de10</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, S3, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,94 +2456,94 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac0b8be0e4857da6</t>
+          <t>https://www.indeed.com/viewjob?jk=9d2302c7e6b6aaf2</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Developer Operations Engineer I</t>
+          <t>Senior DevOps Engineer, US Production</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Transcor Data Services</t>
+          <t>Zafran Security</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b84e13a37c8822b9</t>
+          <t>https://www.indeed.com/viewjob?jk=ab3c0d8531de480d</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr Data Scientist - Member Growth &amp; Prescreen Modeling</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Tukwila, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Snowflake, MLOps</t>
+          <t>AWS, S3, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93bbd48d3322e5c7</t>
+          <t>https://www.indeed.com/viewjob?jk=90ffeeb2227958d7</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer - Hybrid</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Univision Communications Inc</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, IAM, Google Cloud Platform, GCP, Hadoop, Spark, Scala, dbt, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Google Cloud Platform, GCP</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2f885fbfd483879</t>
+          <t>https://www.indeed.com/viewjob?jk=6c3e33c47a701cd2</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Platform Software Engineer</t>
+          <t>Senior Software Engineer - Hybrid</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, CI/CD, Kubernetes, Airflow, Apache Airflow, Git</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Google Cloud Platform, GCP</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a25c9133cd0e70a2</t>
+          <t>https://www.indeed.com/viewjob?jk=03e620dabe0cd123</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>El Pollo Loco</t>
+          <t>Ameriprise Financial</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, SQL Server, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Dataflow, Oracle, SQL Server, PostgreSQL, ETL, MLOps</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bd72bf197f82e23</t>
+          <t>https://www.indeed.com/viewjob?jk=2dc316693a524ae7</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Orchestration</t>
+          <t>Senior Software Engineer | Middleware</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Arvest Bank</t>
+          <t>ExtraHop Networks</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Dataflow, Scala, Kafka, ETL, dbt, Tableau, Docker</t>
+          <t>AWS, S3, SQS, IAM, RDS, Azure, GCP, Scala, PostgreSQL, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8fe7267b8b9de10</t>
+          <t>https://www.indeed.com/viewjob?jk=111ecbafdd773723</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Ulta</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, S3, Spark, PySpark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,67 +2701,67 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d2302c7e6b6aaf2</t>
+          <t>https://www.indeed.com/viewjob?jk=371cb08487cb7590</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Big Data Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90ffeeb2227958d7</t>
+          <t>https://www.indeed.com/viewjob?jk=a57c804e0f6cdd8d</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Hybrid</t>
+          <t>Junior Analytics Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>SewerAI</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Walnut Creek, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Google Cloud Platform, GCP</t>
+          <t>AWS, Redshift, S3, IAM, RDS, BigQuery, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c3e33c47a701cd2</t>
+          <t>https://www.indeed.com/viewjob?jk=ef23c8da578678cc</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Hybrid</t>
+          <t>Data Engineer - 2 Openings</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Blood Cancer United</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Google Cloud Platform, GCP</t>
+          <t>AWS, S3, RDS, Azure, Blob Storage, GCP, Scala, Snowflake, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e620dabe0cd123</t>
+          <t>https://www.indeed.com/viewjob?jk=dd9f154e39bab643</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Python AI Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Ameriprise Financial</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Dataflow, Oracle, SQL Server, PostgreSQL, ETL, MLOps</t>
+          <t>Kafka, PostgreSQL, ETL, CI/CD, Jenkins, Maven, Docker, Jenkins, pytest, Airflow</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,19 +2841,19 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dc316693a524ae7</t>
+          <t>https://www.indeed.com/viewjob?jk=277d01c969e4d645</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Engineer | Middleware</t>
+          <t>Data Bricks Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ExtraHop Networks</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2862,11 +2862,11 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, IAM, RDS, Azure, GCP, Scala, PostgreSQL, Terraform</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=111ecbafdd773723</t>
+          <t>https://www.indeed.com/viewjob?jk=834e54031f069664</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Cloud Security Engineer</t>
+          <t>Sr RPA Process Automation Developer (UIPATH)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Ulta</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=371cb08487cb7590</t>
+          <t>https://www.indeed.com/viewjob?jk=23d1d78d2eac45da</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Big Data Software Engineer - Remote</t>
+          <t>Sr BI Analyst</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Mizkan America</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,42 +2936,42 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>RDS, Azure, Synapse Analytics, Dataflow, Spark, PySpark, Scala, Data Modeling, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a57c804e0f6cdd8d</t>
+          <t>https://www.indeed.com/viewjob?jk=4207b3535cb26a9b</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Junior Analytics Engineer</t>
+          <t>MuleSoft QA Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SewerAI</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Walnut Creek, CA, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, BigQuery, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,67 +2981,67 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef23c8da578678cc</t>
+          <t>https://www.indeed.com/viewjob?jk=8ec42b333047dabf</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer - 2 Openings</t>
+          <t>Site Reliability Engineer III</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Blood Cancer United</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Blob Storage, GCP, Scala, Snowflake, Data Modeling, Kimball</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Splunk, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd9f154e39bab643</t>
+          <t>https://www.indeed.com/viewjob?jk=08f29a39eb33f231</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Python AI Engineer</t>
+          <t>Sustainability Data and AI Consultant</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Kafka, PostgreSQL, ETL, CI/CD, Jenkins, Maven, Docker, Jenkins, pytest, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Git, Python</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=277d01c969e4d645</t>
+          <t>https://www.indeed.com/viewjob?jk=bc927e4fc5649b27</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Bricks Data Engineer</t>
+          <t>Software Engineer ll, Data Platform</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Cohere Health</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, EMR, Athena, S3, RDS, Scala, Kafka, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=834e54031f069664</t>
+          <t>https://www.indeed.com/viewjob?jk=80e694b601457a09</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Sr RPA Process Automation Developer (UIPATH)</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23d1d78d2eac45da</t>
+          <t>https://www.indeed.com/viewjob?jk=04b2fdcc099c4491</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Engineer III</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Visual Comfort &amp; Co</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,59 +3156,59 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=276c91b178e50bc3</t>
+          <t>https://www.indeed.com/viewjob?jk=ed6f23c724c8deb1</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Sr BI Analyst</t>
+          <t>MuleSoft Developer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Mizkan America</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Dataflow, Spark, PySpark, Scala, Data Modeling, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, Oracle, SQL Server, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4207b3535cb26a9b</t>
+          <t>https://www.indeed.com/viewjob?jk=2aedb694782bdb77</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>MuleSoft QA Engineer</t>
+          <t>Digital Services Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>Continental</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Clinton, MD, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, NoSQL, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ec42b333047dabf</t>
+          <t>https://www.indeed.com/viewjob?jk=92b28fa10f3665b6</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Blaine, MN, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Splunk, Kubernetes, Datadog</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08f29a39eb33f231</t>
+          <t>https://www.indeed.com/viewjob?jk=171a3405a6bf87d5</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sustainability Data and AI Consultant</t>
+          <t>AI Systems Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Git, Python</t>
+          <t>AWS, SQS, SNS, IAM, RDS, Databricks, Scala, Kafka, Databricks Lakehouse, NoSQL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc927e4fc5649b27</t>
+          <t>https://www.indeed.com/viewjob?jk=c00f3c6eabf7aab0</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Engineer ll, Data Platform</t>
+          <t>Security Platform Engineer 2 (Hybrid - Seattle)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Cohere Health</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, EMR, Athena, S3, RDS, Scala, Kafka, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3330,321 +3330,6 @@
         </is>
       </c>
       <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=80e694b601457a09</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Sustainability Data and AI Consultant</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Git, Python</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7976a31d4fb905fe</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Engineer</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Cognizant</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Eden Prairie, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=04b2fdcc099c4491</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>AI Engineer III</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Visual Comfort &amp; Co</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI, Python</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ed6f23c724c8deb1</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>MuleSoft Developer</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>UniFirst</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Wilmington, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, Oracle, SQL Server, NoSQL, Splunk, CI/CD</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2aedb694782bdb77</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Digital Services Engineer</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Continental</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Clinton, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, NoSQL, Docker, Kubernetes, Git, Python</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=92b28fa10f3665b6</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Snowflake Architect</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Cognizant</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Blaine, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=171a3405a6bf87d5</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>AI Systems Engineer</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Suffolk Construction</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>AWS, SQS, SNS, IAM, RDS, Databricks, Scala, Kafka, Databricks Lakehouse, NoSQL</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c00f3c6eabf7aab0</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Software Engineering Supervisor - Hybrid</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Sunrise Banks</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Saint Paul, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, NoSQL, CI/CD, Azure DevOps, Git</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=853197679fd8570c</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Security Platform Engineer 2 (Hybrid - Seattle)</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Nordstrom</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=49744f4cb7f46ca9</t>
         </is>

--- a/results/job_matches_2026-06-27.xlsx
+++ b/results/job_matches_2026-06-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G83"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1133,17 +1133,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior IT Big Data Developer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Centurion Consulting Group</t>
+          <t>retail services &amp; systems</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>RDS, Databricks, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae26c12caca27959</t>
+          <t>https://www.indeed.com/viewjob?jk=0f105ffde2d1f4df</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Software Engineer - Platform</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>retail services &amp; systems</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f105ffde2d1f4df</t>
+          <t>https://www.indeed.com/viewjob?jk=3ecc89ba914fc587</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Platform</t>
+          <t>Senior BI Developer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Foundation Building Materials</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, Dataflow, Spark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ecc89ba914fc587</t>
+          <t>https://www.indeed.com/viewjob?jk=25c1cd979546661c</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior BI Developer</t>
+          <t>Senior Engineer, Invest Tech</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Foundation Building Materials</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, Dataflow, Spark, Scala, SQL Server</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25c1cd979546661c</t>
+          <t>https://www.indeed.com/viewjob?jk=efdcc6d0c28ecda9</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Architect (173743)</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Energy Services Group</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, Scala, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9545b3f6e705f68</t>
+          <t>https://www.indeed.com/viewjob?jk=22692d347007686c</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efdcc6d0c28ecda9</t>
+          <t>https://www.indeed.com/viewjob?jk=418fe6804d9bbee5</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Engineer, Invest Tech</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Energy Services Group</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22692d347007686c</t>
+          <t>https://www.indeed.com/viewjob?jk=455cbc0d06bec7dd</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Engineer, Invest Tech</t>
+          <t>Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=418fe6804d9bbee5</t>
+          <t>https://www.indeed.com/viewjob?jk=861d82e3c9e267af</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Engineer, Invest Tech</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=455cbc0d06bec7dd</t>
+          <t>https://www.indeed.com/viewjob?jk=563ad203b5a2853e</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=861d82e3c9e267af</t>
+          <t>https://www.indeed.com/viewjob?jk=9c88857b2990a629</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32c289c0954d3b83</t>
+          <t>https://www.indeed.com/viewjob?jk=6c30d6189ed53ff4</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=563ad203b5a2853e</t>
+          <t>https://www.indeed.com/viewjob?jk=c9f1090e8d875682</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c88857b2990a629</t>
+          <t>https://www.indeed.com/viewjob?jk=09009f7e617a8382</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c30d6189ed53ff4</t>
+          <t>https://www.indeed.com/viewjob?jk=b3c113a0ea31c0ed</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9f1090e8d875682</t>
+          <t>https://www.indeed.com/viewjob?jk=d5962eb966972f6e</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Software Engineer 2 - Full Stack</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09009f7e617a8382</t>
+          <t>https://www.indeed.com/viewjob?jk=69e822c1cf66e308</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Software Engineer 2 - Full Stack</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3c113a0ea31c0ed</t>
+          <t>https://www.indeed.com/viewjob?jk=37dbcc8bf6973335</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Software Engineer 2 - Full Stack</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5962eb966972f6e</t>
+          <t>https://www.indeed.com/viewjob?jk=d84fecedb12dd363</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69e822c1cf66e308</t>
+          <t>https://www.indeed.com/viewjob?jk=abe999fc3b54fcb4</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Full Stack</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37dbcc8bf6973335</t>
+          <t>https://www.indeed.com/viewjob?jk=b49f50dbf2988c82</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Full Stack</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d84fecedb12dd363</t>
+          <t>https://www.indeed.com/viewjob?jk=d75b791cf50c1184</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Full Stack</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,17 +1886,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abe999fc3b54fcb4</t>
+          <t>https://www.indeed.com/viewjob?jk=776060619ca92d8b</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b49f50dbf2988c82</t>
+          <t>https://www.indeed.com/viewjob?jk=2362abd894783c27</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,129 +1966,129 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d75b791cf50c1184</t>
+          <t>https://www.indeed.com/viewjob?jk=992a2c5f94075440</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Prin Software Engineer - AFS</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Metropolitan Council of the Twin Cities</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=776060619ca92d8b</t>
+          <t>https://www.indeed.com/viewjob?jk=4459c55264602070</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Fubo</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2362abd894783c27</t>
+          <t>https://www.indeed.com/viewjob?jk=0e24be3cd83341f1</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=992a2c5f94075440</t>
+          <t>https://www.indeed.com/viewjob?jk=8122e2600ab1407a</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Engineering</t>
+          <t>Data Platform Engineer (Associate)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Fubo</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e24be3cd83341f1</t>
+          <t>https://www.indeed.com/viewjob?jk=52b81f936f231329</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>IT Software Engineer II</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Yusen Logistics</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8122e2600ab1407a</t>
+          <t>https://www.indeed.com/viewjob?jk=d97e3542d74962da</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Platform Engineer (Associate)</t>
+          <t>IT Software Engineer II</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>Yusen Logistics</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52b81f936f231329</t>
+          <t>https://www.indeed.com/viewjob?jk=ef2fe730515dbece</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>IT Software Engineer II</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Yusen Logistics</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins</t>
+          <t>Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d97e3542d74962da</t>
+          <t>https://www.indeed.com/viewjob?jk=ac0b8be0e4857da6</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>IT Software Engineer II</t>
+          <t>Sr Data Scientist - Member Growth &amp; Prescreen Modeling</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Yusen Logistics</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Tukwila, WA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef2fe730515dbece</t>
+          <t>https://www.indeed.com/viewjob?jk=93bbd48d3322e5c7</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Data Platform Software Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, CI/CD, Kubernetes, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac0b8be0e4857da6</t>
+          <t>https://www.indeed.com/viewjob?jk=a25c9133cd0e70a2</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr Data Scientist - Member Growth &amp; Prescreen Modeling</t>
+          <t>Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>El Pollo Loco</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Tukwila, WA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Snowflake, MLOps</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, SQL Server, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93bbd48d3322e5c7</t>
+          <t>https://www.indeed.com/viewjob?jk=8bd72bf197f82e23</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Platform Software Engineer</t>
+          <t>Senior Data Engineer - Orchestration</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>Arvest Bank</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, CI/CD, Kubernetes, Airflow, Apache Airflow, Git</t>
+          <t>AWS, RDS, GCP, Dataflow, Scala, Kafka, ETL, dbt, Tableau, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a25c9133cd0e70a2</t>
+          <t>https://www.indeed.com/viewjob?jk=e8fe7267b8b9de10</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>El Pollo Loco</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, SQL Server, DynamoDB, CI/CD</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, S3, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,19 +2386,19 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bd72bf197f82e23</t>
+          <t>https://www.indeed.com/viewjob?jk=9d2302c7e6b6aaf2</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Orchestration</t>
+          <t>Senior DevOps Engineer, US Production</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Arvest Bank</t>
+          <t>Zafran Security</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Dataflow, Scala, Kafka, ETL, dbt, Tableau, Docker</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8fe7267b8b9de10</t>
+          <t>https://www.indeed.com/viewjob?jk=ab3c0d8531de480d</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, S3, Spark, PySpark, Scala</t>
+          <t>AWS, S3, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d2302c7e6b6aaf2</t>
+          <t>https://www.indeed.com/viewjob?jk=90ffeeb2227958d7</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer, US Production</t>
+          <t>Senior Software Engineer - Hybrid</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Zafran Security</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Google Cloud Platform, GCP</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab3c0d8531de480d</t>
+          <t>https://www.indeed.com/viewjob?jk=6c3e33c47a701cd2</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Software Engineer - Hybrid</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Google Cloud Platform, GCP</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90ffeeb2227958d7</t>
+          <t>https://www.indeed.com/viewjob?jk=03e620dabe0cd123</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Hybrid</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Ameriprise Financial</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Google Cloud Platform, GCP</t>
+          <t>AWS, RDS, Azure, GCP, Dataflow, Oracle, SQL Server, PostgreSQL, ETL, MLOps</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c3e33c47a701cd2</t>
+          <t>https://www.indeed.com/viewjob?jk=2dc316693a524ae7</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Hybrid</t>
+          <t>Senior Software Engineer | Middleware</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>ExtraHop Networks</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Google Cloud Platform, GCP</t>
+          <t>AWS, S3, SQS, IAM, RDS, Azure, GCP, Scala, PostgreSQL, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e620dabe0cd123</t>
+          <t>https://www.indeed.com/viewjob?jk=111ecbafdd773723</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Ameriprise Financial</t>
+          <t>Ulta</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Dataflow, Oracle, SQL Server, PostgreSQL, ETL, MLOps</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dc316693a524ae7</t>
+          <t>https://www.indeed.com/viewjob?jk=371cb08487cb7590</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Engineer | Middleware</t>
+          <t>Senior Big Data Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ExtraHop Networks</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, IAM, RDS, Azure, GCP, Scala, PostgreSQL, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=111ecbafdd773723</t>
+          <t>https://www.indeed.com/viewjob?jk=a57c804e0f6cdd8d</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Cloud Security Engineer</t>
+          <t>Junior Analytics Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Ulta</t>
+          <t>SewerAI</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>Walnut Creek, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD</t>
+          <t>AWS, Redshift, S3, IAM, RDS, BigQuery, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=371cb08487cb7590</t>
+          <t>https://www.indeed.com/viewjob?jk=ef23c8da578678cc</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Big Data Software Engineer - Remote</t>
+          <t>Data Engineer - 2 Openings</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Blood Cancer United</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, S3, RDS, Azure, Blob Storage, GCP, Scala, Snowflake, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a57c804e0f6cdd8d</t>
+          <t>https://www.indeed.com/viewjob?jk=dd9f154e39bab643</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Junior Analytics Engineer</t>
+          <t>Python AI Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SewerAI</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Walnut Creek, CA, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, BigQuery, Snowflake, ETL, ELT, dbt</t>
+          <t>Kafka, PostgreSQL, ETL, CI/CD, Jenkins, Maven, Docker, Jenkins, pytest, Airflow</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef23c8da578678cc</t>
+          <t>https://www.indeed.com/viewjob?jk=277d01c969e4d645</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer - 2 Openings</t>
+          <t>Data Bricks Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Blood Cancer United</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Blob Storage, GCP, Scala, Snowflake, Data Modeling, Kimball</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd9f154e39bab643</t>
+          <t>https://www.indeed.com/viewjob?jk=834e54031f069664</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Python AI Engineer</t>
+          <t>Sr RPA Process Automation Developer (UIPATH)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Kafka, PostgreSQL, ETL, CI/CD, Jenkins, Maven, Docker, Jenkins, pytest, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=277d01c969e4d645</t>
+          <t>https://www.indeed.com/viewjob?jk=23d1d78d2eac45da</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Bricks Data Engineer</t>
+          <t>Sr BI Analyst</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Mizkan America</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,42 +2866,42 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Synapse Analytics, Dataflow, Spark, PySpark, Scala, Data Modeling, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=834e54031f069664</t>
+          <t>https://www.indeed.com/viewjob?jk=4207b3535cb26a9b</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sr RPA Process Automation Developer (UIPATH)</t>
+          <t>MuleSoft QA Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,59 +2911,59 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23d1d78d2eac45da</t>
+          <t>https://www.indeed.com/viewjob?jk=8ec42b333047dabf</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sr BI Analyst</t>
+          <t>Site Reliability Engineer III</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Mizkan America</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Dataflow, Spark, PySpark, Scala, Data Modeling, Power BI, CI/CD</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Splunk, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4207b3535cb26a9b</t>
+          <t>https://www.indeed.com/viewjob?jk=08f29a39eb33f231</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>MuleSoft QA Engineer</t>
+          <t>Sustainability Data and AI Consultant</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Git, Python</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ec42b333047dabf</t>
+          <t>https://www.indeed.com/viewjob?jk=bc927e4fc5649b27</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III</t>
+          <t>Software Engineer ll, Data Platform</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Cohere Health</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Splunk, Kubernetes, Datadog</t>
+          <t>AWS, EMR, Athena, S3, RDS, Scala, Kafka, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08f29a39eb33f231</t>
+          <t>https://www.indeed.com/viewjob?jk=80e694b601457a09</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sustainability Data and AI Consultant</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Git, Python</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc927e4fc5649b27</t>
+          <t>https://www.indeed.com/viewjob?jk=04b2fdcc099c4491</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Engineer ll, Data Platform</t>
+          <t>AI Engineer III</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Cohere Health</t>
+          <t>Visual Comfort &amp; Co</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, EMR, Athena, S3, RDS, Scala, Kafka, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80e694b601457a09</t>
+          <t>https://www.indeed.com/viewjob?jk=ed6f23c724c8deb1</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>MuleSoft Developer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, Oracle, SQL Server, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04b2fdcc099c4491</t>
+          <t>https://www.indeed.com/viewjob?jk=2aedb694782bdb77</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>AI Engineer III</t>
+          <t>Digital Services Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Visual Comfort &amp; Co</t>
+          <t>Continental</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Clinton, MD, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI, Python</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, NoSQL, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed6f23c724c8deb1</t>
+          <t>https://www.indeed.com/viewjob?jk=92b28fa10f3665b6</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>MuleSoft Developer</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Blaine, MN, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, Oracle, SQL Server, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2aedb694782bdb77</t>
+          <t>https://www.indeed.com/viewjob?jk=171a3405a6bf87d5</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Digital Services Engineer</t>
+          <t>AI Systems Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Continental</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Clinton, MD, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, NoSQL, Docker, Kubernetes, Git, Python</t>
+          <t>AWS, SQS, SNS, IAM, RDS, Databricks, Scala, Kafka, Databricks Lakehouse, NoSQL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92b28fa10f3665b6</t>
+          <t>https://www.indeed.com/viewjob?jk=c00f3c6eabf7aab0</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>Security Platform Engineer 2 (Hybrid - Seattle)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Blaine, MN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3260,76 +3260,6 @@
         </is>
       </c>
       <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=171a3405a6bf87d5</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>AI Systems Engineer</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Suffolk Construction</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>AWS, SQS, SNS, IAM, RDS, Databricks, Scala, Kafka, Databricks Lakehouse, NoSQL</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c00f3c6eabf7aab0</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Security Platform Engineer 2 (Hybrid - Seattle)</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Nordstrom</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=49744f4cb7f46ca9</t>
         </is>

--- a/results/job_matches_2026-06-27.xlsx
+++ b/results/job_matches_2026-06-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G81"/>
+  <dimension ref="A1:G58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Data</t>
+          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,14 +636,14 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0631739ce734e7c7</t>
+          <t>https://www.indeed.com/viewjob?jk=2158d7493af1e09e</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing</t>
+          <t>Sr. Specialist Solutions Architect - Data Engineering &amp; Warehousing</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2158d7493af1e09e</t>
+          <t>https://www.indeed.com/viewjob?jk=35b4bec9ddbc42a3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr. Specialist Solutions Architect - Data Engineering &amp; Warehousing</t>
+          <t>Senior API Cloud Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Transflo</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,67 +706,67 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35b4bec9ddbc42a3</t>
+          <t>https://www.indeed.com/viewjob?jk=c6877ccbd8db8810</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior API Cloud Engineer</t>
+          <t>Senior IT Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Transflo</t>
+          <t>Diverse Agile Solutions</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
+          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6877ccbd8db8810</t>
+          <t>https://www.indeed.com/viewjob?jk=445f550d4f69a7c6</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Mainframe Analyst (Healthcare)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NSV IT SOLUTIONS</t>
+          <t>Networking for Future, Inc.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Step Functions, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=529186dc1f0e5461</t>
+          <t>https://www.indeed.com/viewjob?jk=0b36615465054406</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior IT Data Engineer</t>
+          <t>Quant Analytics Associate Sr - DART</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Diverse Agile Solutions</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,77 +801,77 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, ETL, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=445f550d4f69a7c6</t>
+          <t>https://www.indeed.com/viewjob?jk=958563c6ca41d7c8</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Quant Analytics Associate Sr - DART</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, ETL, ELT, dbt, Tableau</t>
+          <t>AWS, Lambda, Kinesis, Athena, IAM, RDS, Databricks, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=958563c6ca41d7c8</t>
+          <t>https://www.indeed.com/viewjob?jk=feff26b7bae36907</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Networking for Future, Inc.</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL</t>
+          <t>AWS, Lambda, Kinesis, Athena, IAM, RDS, Databricks, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b36615465054406</t>
+          <t>https://www.indeed.com/viewjob?jk=694cbe94ae40ae5b</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feff26b7bae36907</t>
+          <t>https://www.indeed.com/viewjob?jk=a0f4bf7cb698e418</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=694cbe94ae40ae5b</t>
+          <t>https://www.indeed.com/viewjob?jk=48492fee574585c7</t>
         </is>
       </c>
     </row>
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0f4bf7cb698e418</t>
+          <t>https://www.indeed.com/viewjob?jk=6a3e9b920b8a4519</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Sr. IT Big Data Developer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Diverse Agile Solutions</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,17 +1011,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Athena, IAM, RDS, Databricks, Scala, Snowflake, ETL</t>
+          <t>AWS, Step Functions, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48492fee574585c7</t>
+          <t>https://www.indeed.com/viewjob?jk=dba4bfa4195a614f</t>
         </is>
       </c>
     </row>
@@ -1033,20 +1033,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>retail services &amp; systems</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Athena, IAM, RDS, Databricks, Scala, Snowflake, ETL</t>
+          <t>RDS, Databricks, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a3e9b920b8a4519</t>
+          <t>https://www.indeed.com/viewjob?jk=0f105ffde2d1f4df</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Architect – Washington, DC</t>
+          <t>Senior Software Engineer - Platform</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Creative Information Technology India</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Falls Church, VA, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,67 +1091,67 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94d5786e7c110147</t>
+          <t>https://www.indeed.com/viewjob?jk=3ecc89ba914fc587</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr. IT Big Data Developer</t>
+          <t>Senior BI Developer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Diverse Agile Solutions</t>
+          <t>Foundation Building Materials</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, Dataflow, Spark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dba4bfa4195a614f</t>
+          <t>https://www.indeed.com/viewjob?jk=25c1cd979546661c</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Engineer, Invest Tech</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>retail services &amp; systems</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake, Dimensional Modeling, ETL</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f105ffde2d1f4df</t>
+          <t>https://www.indeed.com/viewjob?jk=efdcc6d0c28ecda9</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Platform</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Energy Services Group</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ecc89ba914fc587</t>
+          <t>https://www.indeed.com/viewjob?jk=22692d347007686c</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior BI Developer</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Foundation Building Materials</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, Dataflow, Spark, Scala, SQL Server</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25c1cd979546661c</t>
+          <t>https://www.indeed.com/viewjob?jk=563ad203b5a2853e</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Engineer, Invest Tech</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efdcc6d0c28ecda9</t>
+          <t>https://www.indeed.com/viewjob?jk=9c88857b2990a629</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Energy Services Group</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,19 +1301,19 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22692d347007686c</t>
+          <t>https://www.indeed.com/viewjob?jk=6c30d6189ed53ff4</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Engineer, Invest Tech</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=418fe6804d9bbee5</t>
+          <t>https://www.indeed.com/viewjob?jk=c9f1090e8d875682</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Engineer, Invest Tech</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=455cbc0d06bec7dd</t>
+          <t>https://www.indeed.com/viewjob?jk=09009f7e617a8382</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=861d82e3c9e267af</t>
+          <t>https://www.indeed.com/viewjob?jk=b3c113a0ea31c0ed</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=563ad203b5a2853e</t>
+          <t>https://www.indeed.com/viewjob?jk=d5962eb966972f6e</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Software Engineer 2 - Full Stack</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c88857b2990a629</t>
+          <t>https://www.indeed.com/viewjob?jk=69e822c1cf66e308</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Software Engineer 2 - Full Stack</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c30d6189ed53ff4</t>
+          <t>https://www.indeed.com/viewjob?jk=37dbcc8bf6973335</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Software Engineer 2 - Full Stack</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9f1090e8d875682</t>
+          <t>https://www.indeed.com/viewjob?jk=d84fecedb12dd363</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Software Engineer 2 - Full Stack</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09009f7e617a8382</t>
+          <t>https://www.indeed.com/viewjob?jk=abe999fc3b54fcb4</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3c113a0ea31c0ed</t>
+          <t>https://www.indeed.com/viewjob?jk=8122e2600ab1407a</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Data Platform Engineer (Associate)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5962eb966972f6e</t>
+          <t>https://www.indeed.com/viewjob?jk=52b81f936f231329</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Full Stack</t>
+          <t>Prin Software Engineer - AFS</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Metropolitan Council of the Twin Cities</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69e822c1cf66e308</t>
+          <t>https://www.indeed.com/viewjob?jk=4459c55264602070</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Full Stack</t>
+          <t>IT Software Engineer II</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Yusen Logistics</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37dbcc8bf6973335</t>
+          <t>https://www.indeed.com/viewjob?jk=d97e3542d74962da</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Full Stack</t>
+          <t>IT Software Engineer II</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Yusen Logistics</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d84fecedb12dd363</t>
+          <t>https://www.indeed.com/viewjob?jk=ef2fe730515dbece</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Full Stack</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,207 +1791,207 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abe999fc3b54fcb4</t>
+          <t>https://www.indeed.com/viewjob?jk=ac0b8be0e4857da6</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Data Scientist - Member Growth &amp; Prescreen Modeling</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Tukwila, WA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b49f50dbf2988c82</t>
+          <t>https://www.indeed.com/viewjob?jk=93bbd48d3322e5c7</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Platform Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, CI/CD, Kubernetes, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d75b791cf50c1184</t>
+          <t>https://www.indeed.com/viewjob?jk=a25c9133cd0e70a2</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>El Pollo Loco</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, SQL Server, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=776060619ca92d8b</t>
+          <t>https://www.indeed.com/viewjob?jk=8bd72bf197f82e23</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2362abd894783c27</t>
+          <t>https://www.indeed.com/viewjob?jk=90ffeeb2227958d7</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior DevOps Engineer, US Production</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Zafran Security</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=992a2c5f94075440</t>
+          <t>https://www.indeed.com/viewjob?jk=ab3c0d8531de480d</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Prin Software Engineer - AFS</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Metropolitan Council of the Twin Cities</t>
+          <t>Ameriprise Financial</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Dataflow, Oracle, SQL Server, PostgreSQL, ETL, MLOps</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4459c55264602070</t>
+          <t>https://www.indeed.com/viewjob?jk=2dc316693a524ae7</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Engineering</t>
+          <t>Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Fubo</t>
+          <t>Ulta</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e24be3cd83341f1</t>
+          <t>https://www.indeed.com/viewjob?jk=371cb08487cb7590</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Junior Analytics Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>SewerAI</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Walnut Creek, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, Redshift, S3, IAM, RDS, BigQuery, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8122e2600ab1407a</t>
+          <t>https://www.indeed.com/viewjob?jk=ef23c8da578678cc</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Platform Engineer (Associate)</t>
+          <t>Senior Big Data Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52b81f936f231329</t>
+          <t>https://www.indeed.com/viewjob?jk=a57c804e0f6cdd8d</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>IT Software Engineer II</t>
+          <t>Sr RPA Process Automation Developer (UIPATH)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Yusen Logistics</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,102 +2141,102 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d97e3542d74962da</t>
+          <t>https://www.indeed.com/viewjob?jk=23d1d78d2eac45da</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>IT Software Engineer II</t>
+          <t>Sr BI Analyst</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Yusen Logistics</t>
+          <t>Mizkan America</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Synapse Analytics, Dataflow, Spark, PySpark, Scala, Data Modeling, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef2fe730515dbece</t>
+          <t>https://www.indeed.com/viewjob?jk=4207b3535cb26a9b</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Site Reliability Engineer III</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Splunk, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac0b8be0e4857da6</t>
+          <t>https://www.indeed.com/viewjob?jk=08f29a39eb33f231</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr Data Scientist - Member Growth &amp; Prescreen Modeling</t>
+          <t>Sustainability Data and AI Consultant</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Tukwila, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Snowflake, MLOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Git, Python</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93bbd48d3322e5c7</t>
+          <t>https://www.indeed.com/viewjob?jk=bc927e4fc5649b27</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Platform Software Engineer</t>
+          <t>MuleSoft QA Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, CI/CD, Kubernetes, Airflow, Apache Airflow, Git</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a25c9133cd0e70a2</t>
+          <t>https://www.indeed.com/viewjob?jk=8ec42b333047dabf</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>El Pollo Loco</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, SQL Server, DynamoDB, CI/CD</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bd72bf197f82e23</t>
+          <t>https://www.indeed.com/viewjob?jk=04b2fdcc099c4491</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Orchestration</t>
+          <t>AI Engineer III</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Arvest Bank</t>
+          <t>Visual Comfort &amp; Co</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Dataflow, Scala, Kafka, ETL, dbt, Tableau, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8fe7267b8b9de10</t>
+          <t>https://www.indeed.com/viewjob?jk=ed6f23c724c8deb1</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>MuleSoft Developer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, S3, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, Oracle, SQL Server, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,880 +2386,75 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d2302c7e6b6aaf2</t>
+          <t>https://www.indeed.com/viewjob?jk=2aedb694782bdb77</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer, US Production</t>
+          <t>AI Systems Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Zafran Security</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, SQS, SNS, IAM, RDS, Databricks, Scala, Kafka, Databricks Lakehouse, NoSQL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab3c0d8531de480d</t>
+          <t>https://www.indeed.com/viewjob?jk=c00f3c6eabf7aab0</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Security Platform Engineer 2 (Hybrid - Seattle)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=90ffeeb2227958d7</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Hybrid</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>The Hartford</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Hartford, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Google Cloud Platform, GCP</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6c3e33c47a701cd2</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Hybrid</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>The Hartford</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Google Cloud Platform, GCP</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=03e620dabe0cd123</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Systems Engineer</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Ameriprise Financial</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Minneapolis, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Dataflow, Oracle, SQL Server, PostgreSQL, ETL, MLOps</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2dc316693a524ae7</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer | Middleware</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>ExtraHop Networks</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>AWS, S3, SQS, IAM, RDS, Azure, GCP, Scala, PostgreSQL, Terraform</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=111ecbafdd773723</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Cloud Security Engineer</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Ulta</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Bolingbrook, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=371cb08487cb7590</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Senior Big Data Software Engineer - Remote</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Eden Prairie, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a57c804e0f6cdd8d</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Junior Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>SewerAI</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Walnut Creek, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, S3, IAM, RDS, BigQuery, Snowflake, ETL, ELT, dbt</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ef23c8da578678cc</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Data Engineer - 2 Openings</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Blood Cancer United</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, Blob Storage, GCP, Scala, Snowflake, Data Modeling, Kimball</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dd9f154e39bab643</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Python AI Engineer</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Sunrise, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Kafka, PostgreSQL, ETL, CI/CD, Jenkins, Maven, Docker, Jenkins, pytest, Airflow</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=277d01c969e4d645</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Data Bricks Data Engineer</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, ETL, ELT, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=834e54031f069664</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Sr RPA Process Automation Developer (UIPATH)</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Citizens</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Johnston, RI, US USA</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=23d1d78d2eac45da</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Sr BI Analyst</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Mizkan America</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Synapse Analytics, Dataflow, Spark, PySpark, Scala, Data Modeling, Power BI, CI/CD</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4207b3535cb26a9b</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>MuleSoft QA Engineer</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>UniFirst</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Wilmington, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8ec42b333047dabf</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Site Reliability Engineer III</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Splunk, Kubernetes, Datadog</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=08f29a39eb33f231</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Sustainability Data and AI Consultant</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Git, Python</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bc927e4fc5649b27</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Software Engineer ll, Data Platform</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Cohere Health</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>AWS, EMR, Athena, S3, RDS, Scala, Kafka, dbt, CI/CD, Airflow</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=80e694b601457a09</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Engineer</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Cognizant</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Eden Prairie, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=04b2fdcc099c4491</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>AI Engineer III</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Visual Comfort &amp; Co</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI, Python</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ed6f23c724c8deb1</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>MuleSoft Developer</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>UniFirst</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Wilmington, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, Oracle, SQL Server, NoSQL, Splunk, CI/CD</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2aedb694782bdb77</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Digital Services Engineer</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Continental</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Clinton, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, NoSQL, Docker, Kubernetes, Git, Python</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=92b28fa10f3665b6</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Snowflake Architect</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Cognizant</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Blaine, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=171a3405a6bf87d5</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>AI Systems Engineer</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Suffolk Construction</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>AWS, SQS, SNS, IAM, RDS, Databricks, Scala, Kafka, Databricks Lakehouse, NoSQL</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c00f3c6eabf7aab0</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Security Platform Engineer 2 (Hybrid - Seattle)</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Nordstrom</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=49744f4cb7f46ca9</t>
         </is>

--- a/results/job_matches_2026-06-27.xlsx
+++ b/results/job_matches_2026-06-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G58"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,87 +468,87 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Engineering</t>
+          <t>Data Engineer (Business Analyst IV)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Resmed</t>
+          <t>Fairfax County Government</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20.8</v>
+        <v>18.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Spark, Scala, Kafka, Snowflake, SQL Server, PostgreSQL</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, BigQuery, Cloud Storage, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db8f881d56beb45b</t>
+          <t>https://www.indeed.com/viewjob?jk=414e38f5ca1fe7f7</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer (Business Analyst IV)</t>
+          <t>Data Engineer C1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Fairfax County Government</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, BigQuery, Cloud Storage, Hadoop, Spark, Scala</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=414e38f5ca1fe7f7</t>
+          <t>https://www.indeed.com/viewjob?jk=797ab0abe77eeb1d</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer C1</t>
+          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Scala, Kafka</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=797ab0abe77eeb1d</t>
+          <t>https://www.indeed.com/viewjob?jk=2158d7493af1e09e</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Specialist Solutions Architect - Data Engineering &amp; Warehousing</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Edwards Lifesciences</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02a96598db050be0</t>
+          <t>https://www.indeed.com/viewjob?jk=35b4bec9ddbc42a3</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing</t>
+          <t>Senior API Cloud Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Transflo</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,67 +636,67 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2158d7493af1e09e</t>
+          <t>https://www.indeed.com/viewjob?jk=c6877ccbd8db8810</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr. Specialist Solutions Architect - Data Engineering &amp; Warehousing</t>
+          <t>Senior IT Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Diverse Agile Solutions</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala</t>
+          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35b4bec9ddbc42a3</t>
+          <t>https://www.indeed.com/viewjob?jk=445f550d4f69a7c6</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior API Cloud Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Transflo</t>
+          <t>Networking for Future, Inc.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
+          <t>AWS, Step Functions, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6877ccbd8db8810</t>
+          <t>https://www.indeed.com/viewjob?jk=0b36615465054406</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior IT Data Engineer</t>
+          <t>Quant Analytics Associate Sr - DART</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Diverse Agile Solutions</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,42 +731,42 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, ETL, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=445f550d4f69a7c6</t>
+          <t>https://www.indeed.com/viewjob?jk=958563c6ca41d7c8</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Networking for Future, Inc.</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL</t>
+          <t>AWS, Lambda, Kinesis, Athena, IAM, RDS, Databricks, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,42 +776,42 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b36615465054406</t>
+          <t>https://www.indeed.com/viewjob?jk=feff26b7bae36907</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Quant Analytics Associate Sr - DART</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, ETL, ELT, dbt, Tableau</t>
+          <t>AWS, Lambda, Kinesis, Athena, IAM, RDS, Databricks, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=958563c6ca41d7c8</t>
+          <t>https://www.indeed.com/viewjob?jk=694cbe94ae40ae5b</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feff26b7bae36907</t>
+          <t>https://www.indeed.com/viewjob?jk=a0f4bf7cb698e418</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=694cbe94ae40ae5b</t>
+          <t>https://www.indeed.com/viewjob?jk=48492fee574585c7</t>
         </is>
       </c>
     </row>
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0f4bf7cb698e418</t>
+          <t>https://www.indeed.com/viewjob?jk=6a3e9b920b8a4519</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Sr. IT Big Data Developer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Diverse Agile Solutions</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,17 +941,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Athena, IAM, RDS, Databricks, Scala, Snowflake, ETL</t>
+          <t>AWS, Step Functions, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48492fee574585c7</t>
+          <t>https://www.indeed.com/viewjob?jk=dba4bfa4195a614f</t>
         </is>
       </c>
     </row>
@@ -963,20 +963,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>retail services &amp; systems</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Athena, IAM, RDS, Databricks, Scala, Snowflake, ETL</t>
+          <t>RDS, Databricks, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,67 +986,67 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a3e9b920b8a4519</t>
+          <t>https://www.indeed.com/viewjob?jk=0f105ffde2d1f4df</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr. IT Big Data Developer</t>
+          <t>Senior Software Engineer - Platform</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Diverse Agile Solutions</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dba4bfa4195a614f</t>
+          <t>https://www.indeed.com/viewjob?jk=3ecc89ba914fc587</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior BI Developer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>retail services &amp; systems</t>
+          <t>Foundation Building Materials</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, Dataflow, Spark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f105ffde2d1f4df</t>
+          <t>https://www.indeed.com/viewjob?jk=25c1cd979546661c</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Platform</t>
+          <t>Senior Engineer, Invest Tech</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ecc89ba914fc587</t>
+          <t>https://www.indeed.com/viewjob?jk=efdcc6d0c28ecda9</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior BI Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Foundation Building Materials</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, Dataflow, Spark, Scala, SQL Server</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25c1cd979546661c</t>
+          <t>https://www.indeed.com/viewjob?jk=8122e2600ab1407a</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Engineer, Invest Tech</t>
+          <t>Prin Software Engineer - AFS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>Metropolitan Council of the Twin Cities</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efdcc6d0c28ecda9</t>
+          <t>https://www.indeed.com/viewjob?jk=4459c55264602070</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>IT Software Engineer II</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Energy Services Group</t>
+          <t>Yusen Logistics</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22692d347007686c</t>
+          <t>https://www.indeed.com/viewjob?jk=d97e3542d74962da</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>IT Software Engineer II</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Yusen Logistics</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=563ad203b5a2853e</t>
+          <t>https://www.indeed.com/viewjob?jk=ef2fe730515dbece</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c88857b2990a629</t>
+          <t>https://www.indeed.com/viewjob?jk=ac0b8be0e4857da6</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Sr Data Scientist - Member Growth &amp; Prescreen Modeling</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Tukwila, WA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c30d6189ed53ff4</t>
+          <t>https://www.indeed.com/viewjob?jk=93bbd48d3322e5c7</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Data Platform Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, CI/CD, Kubernetes, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9f1090e8d875682</t>
+          <t>https://www.indeed.com/viewjob?jk=a25c9133cd0e70a2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>El Pollo Loco</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, SQL Server, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,67 +1371,67 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09009f7e617a8382</t>
+          <t>https://www.indeed.com/viewjob?jk=8bd72bf197f82e23</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3c113a0ea31c0ed</t>
+          <t>https://www.indeed.com/viewjob?jk=90ffeeb2227958d7</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Ameriprise Financial</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Dataflow, Oracle, SQL Server, PostgreSQL, ETL, MLOps</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,67 +1441,67 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5962eb966972f6e</t>
+          <t>https://www.indeed.com/viewjob?jk=2dc316693a524ae7</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Full Stack</t>
+          <t>Senior DevOps Engineer, US Production</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Zafran Security</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69e822c1cf66e308</t>
+          <t>https://www.indeed.com/viewjob?jk=ab3c0d8531de480d</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Full Stack</t>
+          <t>Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Ulta</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37dbcc8bf6973335</t>
+          <t>https://www.indeed.com/viewjob?jk=371cb08487cb7590</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Full Stack</t>
+          <t>Junior Analytics Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>SewerAI</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Walnut Creek, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, Redshift, S3, IAM, RDS, BigQuery, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d84fecedb12dd363</t>
+          <t>https://www.indeed.com/viewjob?jk=ef23c8da578678cc</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Full Stack</t>
+          <t>Senior Big Data Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abe999fc3b54fcb4</t>
+          <t>https://www.indeed.com/viewjob?jk=a57c804e0f6cdd8d</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr RPA Process Automation Developer (UIPATH)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,102 +1616,102 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8122e2600ab1407a</t>
+          <t>https://www.indeed.com/viewjob?jk=23d1d78d2eac45da</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Platform Engineer (Associate)</t>
+          <t>Sr BI Analyst</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>Mizkan America</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Synapse Analytics, Dataflow, Spark, PySpark, Scala, Data Modeling, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52b81f936f231329</t>
+          <t>https://www.indeed.com/viewjob?jk=4207b3535cb26a9b</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Prin Software Engineer - AFS</t>
+          <t>Site Reliability Engineer III</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Metropolitan Council of the Twin Cities</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Splunk, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4459c55264602070</t>
+          <t>https://www.indeed.com/viewjob?jk=08f29a39eb33f231</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>IT Software Engineer II</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Yusen Logistics</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d97e3542d74962da</t>
+          <t>https://www.indeed.com/viewjob?jk=04b2fdcc099c4491</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>IT Software Engineer II</t>
+          <t>AI Engineer III</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Yusen Logistics</t>
+          <t>Visual Comfort &amp; Co</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,67 +1756,67 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef2fe730515dbece</t>
+          <t>https://www.indeed.com/viewjob?jk=ed6f23c724c8deb1</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>AI Systems Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, SQS, SNS, IAM, RDS, Databricks, Scala, Kafka, Databricks Lakehouse, NoSQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac0b8be0e4857da6</t>
+          <t>https://www.indeed.com/viewjob?jk=c00f3c6eabf7aab0</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr Data Scientist - Member Growth &amp; Prescreen Modeling</t>
+          <t>Security Platform Engineer 2 (Hybrid - Seattle)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tukwila, WA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Snowflake, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1825,636 +1825,6 @@
         </is>
       </c>
       <c r="G40" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=93bbd48d3322e5c7</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Data Platform Software Engineer</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>SS&amp;C</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Kansas City, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, CI/CD, Kubernetes, Airflow, Apache Airflow, Git</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a25c9133cd0e70a2</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Infrastructure Engineer</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>El Pollo Loco</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Costa Mesa, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, SQL Server, DynamoDB, CI/CD</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8bd72bf197f82e23</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Data Architect</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=90ffeeb2227958d7</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer, US Production</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Zafran Security</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ab3c0d8531de480d</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Systems Engineer</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Ameriprise Financial</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Minneapolis, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Dataflow, Oracle, SQL Server, PostgreSQL, ETL, MLOps</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2dc316693a524ae7</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Cloud Security Engineer</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Ulta</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Bolingbrook, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=371cb08487cb7590</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Junior Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>SewerAI</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Walnut Creek, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, S3, IAM, RDS, BigQuery, Snowflake, ETL, ELT, dbt</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ef23c8da578678cc</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Senior Big Data Software Engineer - Remote</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Eden Prairie, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a57c804e0f6cdd8d</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Sr RPA Process Automation Developer (UIPATH)</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Citizens</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Johnston, RI, US USA</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=23d1d78d2eac45da</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Sr BI Analyst</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Mizkan America</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Synapse Analytics, Dataflow, Spark, PySpark, Scala, Data Modeling, Power BI, CI/CD</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4207b3535cb26a9b</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Site Reliability Engineer III</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Splunk, Kubernetes, Datadog</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=08f29a39eb33f231</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Sustainability Data and AI Consultant</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, Git, Python</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bc927e4fc5649b27</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>MuleSoft QA Engineer</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>UniFirst</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Wilmington, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8ec42b333047dabf</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Engineer</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Cognizant</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Eden Prairie, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=04b2fdcc099c4491</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>AI Engineer III</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Visual Comfort &amp; Co</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI, Python</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ed6f23c724c8deb1</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>MuleSoft Developer</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>UniFirst</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Wilmington, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, Oracle, SQL Server, NoSQL, Splunk, CI/CD</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2aedb694782bdb77</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>AI Systems Engineer</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Suffolk Construction</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>AWS, SQS, SNS, IAM, RDS, Databricks, Scala, Kafka, Databricks Lakehouse, NoSQL</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c00f3c6eabf7aab0</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Security Platform Engineer 2 (Hybrid - Seattle)</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Nordstrom</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=49744f4cb7f46ca9</t>
         </is>

--- a/results/job_matches_2026-06-27.xlsx
+++ b/results/job_matches_2026-06-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1098,17 +1098,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Prin Software Engineer - AFS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Metropolitan Council of the Twin Cities</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8122e2600ab1407a</t>
+          <t>https://www.indeed.com/viewjob?jk=4459c55264602070</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Prin Software Engineer - AFS</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Metropolitan Council of the Twin Cities</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4459c55264602070</t>
+          <t>https://www.indeed.com/viewjob?jk=8122e2600ab1407a</t>
         </is>
       </c>
     </row>
@@ -1273,25 +1273,25 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr Data Scientist - Member Growth &amp; Prescreen Modeling</t>
+          <t>Data Platform Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Tukwila, WA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Snowflake, MLOps</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, CI/CD, Kubernetes, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93bbd48d3322e5c7</t>
+          <t>https://www.indeed.com/viewjob?jk=a25c9133cd0e70a2</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Platform Software Engineer</t>
+          <t>Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>El Pollo Loco</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, CI/CD, Kubernetes, Airflow, Apache Airflow, Git</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, SQL Server, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a25c9133cd0e70a2</t>
+          <t>https://www.indeed.com/viewjob?jk=8bd72bf197f82e23</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>El Pollo Loco</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, SQL Server, DynamoDB, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bd72bf197f82e23</t>
+          <t>https://www.indeed.com/viewjob?jk=90ffeeb2227958d7</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ameriprise Financial</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Dataflow, Oracle, SQL Server, PostgreSQL, ETL, MLOps</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90ffeeb2227958d7</t>
+          <t>https://www.indeed.com/viewjob?jk=2dc316693a524ae7</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Senior DevOps Engineer, US Production</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Ameriprise Financial</t>
+          <t>Zafran Security</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Dataflow, Oracle, SQL Server, PostgreSQL, ETL, MLOps</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dc316693a524ae7</t>
+          <t>https://www.indeed.com/viewjob?jk=ab3c0d8531de480d</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer, US Production</t>
+          <t>Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Zafran Security</t>
+          <t>Ulta</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,42 +1466,42 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab3c0d8531de480d</t>
+          <t>https://www.indeed.com/viewjob?jk=371cb08487cb7590</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Cloud Security Engineer</t>
+          <t>Junior Analytics Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Ulta</t>
+          <t>SewerAI</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>Walnut Creek, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD</t>
+          <t>AWS, Redshift, S3, IAM, RDS, BigQuery, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=371cb08487cb7590</t>
+          <t>https://www.indeed.com/viewjob?jk=ef23c8da578678cc</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Junior Analytics Engineer</t>
+          <t>Sr RPA Process Automation Developer (UIPATH)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SewerAI</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Walnut Creek, CA, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, BigQuery, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,67 +1546,67 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef23c8da578678cc</t>
+          <t>https://www.indeed.com/viewjob?jk=23d1d78d2eac45da</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Big Data Software Engineer - Remote</t>
+          <t>Site Reliability Engineer III</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Splunk, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a57c804e0f6cdd8d</t>
+          <t>https://www.indeed.com/viewjob?jk=08f29a39eb33f231</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr RPA Process Automation Developer (UIPATH)</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,59 +1616,59 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23d1d78d2eac45da</t>
+          <t>https://www.indeed.com/viewjob?jk=04b2fdcc099c4491</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr BI Analyst</t>
+          <t>AI Engineer III</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Mizkan America</t>
+          <t>Visual Comfort &amp; Co</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Dataflow, Spark, PySpark, Scala, Data Modeling, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4207b3535cb26a9b</t>
+          <t>https://www.indeed.com/viewjob?jk=ed6f23c724c8deb1</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III</t>
+          <t>AI Systems Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Splunk, Kubernetes, Datadog</t>
+          <t>AWS, SQS, SNS, IAM, RDS, Databricks, Scala, Kafka, Databricks Lakehouse, NoSQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08f29a39eb33f231</t>
+          <t>https://www.indeed.com/viewjob?jk=c00f3c6eabf7aab0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Security Platform Engineer 2 (Hybrid - Seattle)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1720,111 +1720,6 @@
         </is>
       </c>
       <c r="G37" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=04b2fdcc099c4491</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>AI Engineer III</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Visual Comfort &amp; Co</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI, Python</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ed6f23c724c8deb1</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>AI Systems Engineer</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Suffolk Construction</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>AWS, SQS, SNS, IAM, RDS, Databricks, Scala, Kafka, Databricks Lakehouse, NoSQL</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c00f3c6eabf7aab0</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Security Platform Engineer 2 (Hybrid - Seattle)</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Nordstrom</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=49744f4cb7f46ca9</t>
         </is>
